--- a/output/yearly_population_iteration_53_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_53_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6285</v>
+        <v>6018</v>
       </c>
       <c r="C2" t="n">
-        <v>13222</v>
+        <v>5808</v>
       </c>
       <c r="D2" t="n">
-        <v>17746</v>
+        <v>23474</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4165</v>
+        <v>3800</v>
       </c>
       <c r="C3" t="n">
-        <v>6478</v>
+        <v>6187</v>
       </c>
       <c r="D3" t="n">
-        <v>12188</v>
+        <v>12713</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3363</v>
+        <v>2836</v>
       </c>
       <c r="C4" t="n">
-        <v>5753</v>
+        <v>7652</v>
       </c>
       <c r="D4" t="n">
-        <v>6369</v>
+        <v>6960</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2194</v>
+        <v>1841</v>
       </c>
       <c r="C5" t="n">
-        <v>3529</v>
+        <v>6427</v>
       </c>
       <c r="D5" t="n">
-        <v>2504</v>
+        <v>3043</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1251</v>
+        <v>1044</v>
       </c>
       <c r="C6" t="n">
-        <v>2182</v>
+        <v>3927</v>
       </c>
       <c r="D6" t="n">
-        <v>1138</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>622</v>
+        <v>472</v>
       </c>
       <c r="C7" t="n">
-        <v>1522</v>
+        <v>2057</v>
       </c>
       <c r="D7" t="n">
-        <v>648</v>
+        <v>684</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>231</v>
+        <v>173</v>
       </c>
       <c r="C8" t="n">
-        <v>774</v>
+        <v>892</v>
       </c>
       <c r="D8" t="n">
-        <v>437</v>
+        <v>435</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="C9" t="n">
-        <v>349</v>
+        <v>367</v>
       </c>
       <c r="D9" t="n">
-        <v>306</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -996,7 +996,7 @@
         <v>38</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1007,7 +1007,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1049,10 +1049,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8463</v>
+        <v>6295</v>
       </c>
       <c r="C2" t="n">
-        <v>11242</v>
+        <v>7856</v>
       </c>
       <c r="D2" t="n">
-        <v>16717</v>
+        <v>19355</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4220</v>
+        <v>3868</v>
       </c>
       <c r="C3" t="n">
-        <v>8441</v>
+        <v>5318</v>
       </c>
       <c r="D3" t="n">
-        <v>12124</v>
+        <v>13256</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3180</v>
+        <v>2793</v>
       </c>
       <c r="C4" t="n">
-        <v>5988</v>
+        <v>6817</v>
       </c>
       <c r="D4" t="n">
-        <v>7063</v>
+        <v>7565</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2391</v>
+        <v>1989</v>
       </c>
       <c r="C5" t="n">
-        <v>4467</v>
+        <v>6772</v>
       </c>
       <c r="D5" t="n">
-        <v>3058</v>
+        <v>3552</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1527</v>
+        <v>1246</v>
       </c>
       <c r="C6" t="n">
-        <v>2780</v>
+        <v>4970</v>
       </c>
       <c r="D6" t="n">
-        <v>1321</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>801</v>
+        <v>630</v>
       </c>
       <c r="C7" t="n">
-        <v>1804</v>
+        <v>2824</v>
       </c>
       <c r="D7" t="n">
-        <v>718</v>
+        <v>770</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>349</v>
+        <v>259</v>
       </c>
       <c r="C8" t="n">
-        <v>1103</v>
+        <v>1371</v>
       </c>
       <c r="D8" t="n">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>125</v>
+        <v>94</v>
       </c>
       <c r="C9" t="n">
-        <v>524</v>
+        <v>569</v>
       </c>
       <c r="D9" t="n">
-        <v>322</v>
+        <v>319</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C10" t="n">
         <v>270</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C11" t="n">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1234,7 +1234,7 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="D12" t="n">
         <v>160</v>
@@ -1248,10 +1248,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1304,10 +1304,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1318,7 +1318,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1360,10 +1360,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>9251</v>
+        <v>6857</v>
       </c>
       <c r="C2" t="n">
-        <v>15974</v>
+        <v>13586</v>
       </c>
       <c r="D2" t="n">
-        <v>19541</v>
+        <v>19504</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4833</v>
+        <v>3922</v>
       </c>
       <c r="C3" t="n">
-        <v>8521</v>
+        <v>5612</v>
       </c>
       <c r="D3" t="n">
-        <v>11916</v>
+        <v>13139</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3082</v>
+        <v>2733</v>
       </c>
       <c r="C4" t="n">
-        <v>6970</v>
+        <v>5990</v>
       </c>
       <c r="D4" t="n">
-        <v>7625</v>
+        <v>8154</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2443</v>
+        <v>2045</v>
       </c>
       <c r="C5" t="n">
-        <v>4988</v>
+        <v>6584</v>
       </c>
       <c r="D5" t="n">
-        <v>3512</v>
+        <v>3949</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1712</v>
+        <v>1396</v>
       </c>
       <c r="C6" t="n">
-        <v>3467</v>
+        <v>5636</v>
       </c>
       <c r="D6" t="n">
-        <v>1553</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>982</v>
+        <v>781</v>
       </c>
       <c r="C7" t="n">
-        <v>2187</v>
+        <v>3615</v>
       </c>
       <c r="D7" t="n">
-        <v>786</v>
+        <v>852</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>467</v>
+        <v>347</v>
       </c>
       <c r="C8" t="n">
-        <v>1373</v>
+        <v>1898</v>
       </c>
       <c r="D8" t="n">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>186</v>
+        <v>133</v>
       </c>
       <c r="C9" t="n">
-        <v>750</v>
+        <v>859</v>
       </c>
       <c r="D9" t="n">
-        <v>333</v>
+        <v>329</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="D10" t="n">
-        <v>255</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C11" t="n">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="D11" t="n">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -1559,7 +1559,7 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D13" t="n">
         <v>128</v>
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="16">
@@ -1601,10 +1601,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -1615,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1629,7 +1629,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8442</v>
+        <v>6395</v>
       </c>
       <c r="C2" t="n">
-        <v>10734</v>
+        <v>9455</v>
       </c>
       <c r="D2" t="n">
-        <v>16090</v>
+        <v>16233</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5714</v>
+        <v>4767</v>
       </c>
       <c r="C3" t="n">
-        <v>13035</v>
+        <v>9388</v>
       </c>
       <c r="D3" t="n">
-        <v>13250</v>
+        <v>14487</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2257</v>
+        <v>1889</v>
       </c>
       <c r="C4" t="n">
-        <v>8669</v>
+        <v>9483</v>
       </c>
       <c r="D4" t="n">
-        <v>7444</v>
+        <v>8052</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1581</v>
+        <v>1289</v>
       </c>
       <c r="C5" t="n">
-        <v>3397</v>
+        <v>5523</v>
       </c>
       <c r="D5" t="n">
-        <v>2499</v>
+        <v>2812</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>907</v>
+        <v>721</v>
       </c>
       <c r="C6" t="n">
-        <v>2143</v>
+        <v>3542</v>
       </c>
       <c r="D6" t="n">
-        <v>770</v>
+        <v>834</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>431</v>
+        <v>320</v>
       </c>
       <c r="C7" t="n">
-        <v>1345</v>
+        <v>1860</v>
       </c>
       <c r="D7" t="n">
-        <v>479</v>
+        <v>484</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>171</v>
+        <v>122</v>
       </c>
       <c r="C8" t="n">
-        <v>735</v>
+        <v>841</v>
       </c>
       <c r="D8" t="n">
-        <v>326</v>
+        <v>322</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="C9" t="n">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="D9" t="n">
-        <v>249</v>
+        <v>244</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="D10" t="n">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="12">
@@ -1856,7 +1856,7 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D12" t="n">
         <v>125</v>
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16">
@@ -1912,10 +1912,10 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D16" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="17">
@@ -1926,7 +1926,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D17" t="n">
         <v>38</v>
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D18" t="n">
         <v>26</v>
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D19" t="n">
         <v>15</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5242</v>
+        <v>3924</v>
       </c>
       <c r="C2" t="n">
-        <v>5170</v>
+        <v>4853</v>
       </c>
       <c r="D2" t="n">
-        <v>11096</v>
+        <v>12096</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>5933</v>
+        <v>4716</v>
       </c>
       <c r="C3" t="n">
-        <v>10847</v>
+        <v>8558</v>
       </c>
       <c r="D3" t="n">
-        <v>12873</v>
+        <v>14029</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3126</v>
+        <v>2563</v>
       </c>
       <c r="C4" t="n">
-        <v>10792</v>
+        <v>9607</v>
       </c>
       <c r="D4" t="n">
-        <v>8252</v>
+        <v>8811</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1756</v>
+        <v>1434</v>
       </c>
       <c r="C5" t="n">
-        <v>5716</v>
+        <v>7178</v>
       </c>
       <c r="D5" t="n">
-        <v>3088</v>
+        <v>3461</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1086</v>
+        <v>844</v>
       </c>
       <c r="C6" t="n">
-        <v>2718</v>
+        <v>4424</v>
       </c>
       <c r="D6" t="n">
-        <v>949</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>406</v>
+        <v>299</v>
       </c>
       <c r="C7" t="n">
-        <v>1668</v>
+        <v>2433</v>
       </c>
       <c r="D7" t="n">
-        <v>522</v>
+        <v>527</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="C8" t="n">
-        <v>952</v>
+        <v>1131</v>
       </c>
       <c r="D8" t="n">
-        <v>340</v>
+        <v>331</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="C9" t="n">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="D9" t="n">
-        <v>258</v>
+        <v>256</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="D10" t="n">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="D11" t="n">
-        <v>166</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15">
@@ -2209,10 +2209,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -2223,7 +2223,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D16" t="n">
         <v>37</v>
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D17" t="n">
         <v>25</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D18" t="n">
         <v>14</v>
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6002</v>
+        <v>4365</v>
       </c>
       <c r="C2" t="n">
-        <v>5546</v>
+        <v>10707</v>
       </c>
       <c r="D2" t="n">
-        <v>11551</v>
+        <v>11347</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4735</v>
+        <v>3697</v>
       </c>
       <c r="C3" t="n">
-        <v>7149</v>
+        <v>6049</v>
       </c>
       <c r="D3" t="n">
-        <v>11855</v>
+        <v>12823</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3747</v>
+        <v>2961</v>
       </c>
       <c r="C4" t="n">
-        <v>10594</v>
+        <v>8903</v>
       </c>
       <c r="D4" t="n">
-        <v>8676</v>
+        <v>9394</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2077</v>
+        <v>1691</v>
       </c>
       <c r="C5" t="n">
-        <v>8088</v>
+        <v>8216</v>
       </c>
       <c r="D5" t="n">
-        <v>3836</v>
+        <v>4177</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1256</v>
+        <v>1001</v>
       </c>
       <c r="C6" t="n">
-        <v>4044</v>
+        <v>5572</v>
       </c>
       <c r="D6" t="n">
-        <v>1264</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>597</v>
+        <v>440</v>
       </c>
       <c r="C7" t="n">
-        <v>2146</v>
+        <v>3294</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>205</v>
+        <v>149</v>
       </c>
       <c r="C8" t="n">
-        <v>1255</v>
+        <v>1652</v>
       </c>
       <c r="D8" t="n">
-        <v>359</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="C9" t="n">
-        <v>622</v>
+        <v>666</v>
       </c>
       <c r="D9" t="n">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="D10" t="n">
-        <v>216</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="D11" t="n">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="13">
@@ -2492,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="D13" t="n">
         <v>100</v>
@@ -2506,7 +2506,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
         <v>62</v>
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D15" t="n">
         <v>48</v>
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D16" t="n">
         <v>36</v>
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3578</v>
+        <v>2649</v>
       </c>
       <c r="C2" t="n">
-        <v>2595</v>
+        <v>5153</v>
       </c>
       <c r="D2" t="n">
-        <v>8056</v>
+        <v>7919</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4861</v>
+        <v>3714</v>
       </c>
       <c r="C3" t="n">
-        <v>6393</v>
+        <v>7316</v>
       </c>
       <c r="D3" t="n">
-        <v>11557</v>
+        <v>12382</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4141</v>
+        <v>3244</v>
       </c>
       <c r="C4" t="n">
-        <v>10266</v>
+        <v>8753</v>
       </c>
       <c r="D4" t="n">
-        <v>9140</v>
+        <v>9895</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2185</v>
+        <v>1745</v>
       </c>
       <c r="C5" t="n">
-        <v>9734</v>
+        <v>9663</v>
       </c>
       <c r="D5" t="n">
-        <v>4031</v>
+        <v>4386</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1062</v>
+        <v>804</v>
       </c>
       <c r="C6" t="n">
-        <v>4903</v>
+        <v>6491</v>
       </c>
       <c r="D6" t="n">
-        <v>1245</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="7">
@@ -2716,10 +2716,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>189</v>
+        <v>137</v>
       </c>
       <c r="C7" t="n">
-        <v>2278</v>
+        <v>3263</v>
       </c>
       <c r="D7" t="n">
         <v>584</v>
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>61</v>
+        <v>46</v>
       </c>
       <c r="C8" t="n">
-        <v>990</v>
+        <v>1138</v>
       </c>
       <c r="D8" t="n">
-        <v>378</v>
+        <v>374</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="D10" t="n">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="D11" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D12" t="n">
         <v>98</v>
@@ -2803,7 +2803,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
         <v>60</v>
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -2831,7 +2831,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D15" t="n">
         <v>35</v>
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4967</v>
+        <v>2755</v>
       </c>
       <c r="C2" t="n">
-        <v>4796</v>
+        <v>6204</v>
       </c>
       <c r="D2" t="n">
-        <v>14156</v>
+        <v>14606</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3699</v>
+        <v>2809</v>
       </c>
       <c r="C3" t="n">
-        <v>4168</v>
+        <v>5672</v>
       </c>
       <c r="D3" t="n">
-        <v>10304</v>
+        <v>10998</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3873</v>
+        <v>3026</v>
       </c>
       <c r="C4" t="n">
-        <v>8230</v>
+        <v>7992</v>
       </c>
       <c r="D4" t="n">
-        <v>9344</v>
+        <v>9976</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2643</v>
+        <v>2068</v>
       </c>
       <c r="C5" t="n">
-        <v>9865</v>
+        <v>9161</v>
       </c>
       <c r="D5" t="n">
-        <v>4644</v>
+        <v>5045</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1362</v>
+        <v>1033</v>
       </c>
       <c r="C6" t="n">
-        <v>6946</v>
+        <v>7776</v>
       </c>
       <c r="D6" t="n">
-        <v>1603</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>401</v>
+        <v>294</v>
       </c>
       <c r="C7" t="n">
-        <v>3376</v>
+        <v>4527</v>
       </c>
       <c r="D7" t="n">
-        <v>667</v>
+        <v>665</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>86</v>
+        <v>61</v>
       </c>
       <c r="C8" t="n">
-        <v>1476</v>
+        <v>1920</v>
       </c>
       <c r="D8" t="n">
-        <v>400</v>
+        <v>396</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>521</v>
+        <v>543</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>290</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="D10" t="n">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="13">
@@ -3114,7 +3114,7 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D13" t="n">
         <v>60</v>
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>44</v>
+      </c>
+      <c r="D14" t="n">
         <v>46</v>
-      </c>
-      <c r="D14" t="n">
-        <v>47</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -3156,7 +3156,7 @@
         <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D16" t="n">
         <v>20</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3643</v>
+        <v>1920</v>
       </c>
       <c r="C2" t="n">
-        <v>3465</v>
+        <v>3730</v>
       </c>
       <c r="D2" t="n">
-        <v>10175</v>
+        <v>10675</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3596</v>
+        <v>2448</v>
       </c>
       <c r="C3" t="n">
-        <v>4047</v>
+        <v>5401</v>
       </c>
       <c r="D3" t="n">
-        <v>10205</v>
+        <v>10821</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3519</v>
+        <v>2730</v>
       </c>
       <c r="C4" t="n">
-        <v>6658</v>
+        <v>7088</v>
       </c>
       <c r="D4" t="n">
-        <v>9368</v>
+        <v>9896</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2850</v>
+        <v>2242</v>
       </c>
       <c r="C5" t="n">
-        <v>9363</v>
+        <v>8918</v>
       </c>
       <c r="D5" t="n">
-        <v>5043</v>
+        <v>5509</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1605</v>
+        <v>1189</v>
       </c>
       <c r="C6" t="n">
-        <v>8135</v>
+        <v>8506</v>
       </c>
       <c r="D6" t="n">
-        <v>1893</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>362</v>
+        <v>262</v>
       </c>
       <c r="C7" t="n">
-        <v>4480</v>
+        <v>5568</v>
       </c>
       <c r="D7" t="n">
-        <v>737</v>
+        <v>741</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>1929</v>
+        <v>2478</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -3380,10 +3380,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="D10" t="n">
         <v>177</v>
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -3411,7 +3411,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="D12" t="n">
         <v>91</v>
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D13" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3453,7 +3453,7 @@
         <v>3</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
         <v>19</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4891</v>
+        <v>3434</v>
       </c>
       <c r="C2" t="n">
-        <v>10063</v>
+        <v>17916</v>
       </c>
       <c r="D2" t="n">
-        <v>8846</v>
+        <v>12158</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3040</v>
+        <v>1914</v>
       </c>
       <c r="C3" t="n">
-        <v>3395</v>
+        <v>4290</v>
       </c>
       <c r="D3" t="n">
-        <v>9548</v>
+        <v>10214</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3081</v>
+        <v>2290</v>
       </c>
       <c r="C4" t="n">
-        <v>5416</v>
+        <v>6260</v>
       </c>
       <c r="D4" t="n">
-        <v>9203</v>
+        <v>9624</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2806</v>
+        <v>2194</v>
       </c>
       <c r="C5" t="n">
-        <v>8077</v>
+        <v>8029</v>
       </c>
       <c r="D5" t="n">
-        <v>5470</v>
+        <v>5931</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1884</v>
+        <v>1423</v>
       </c>
       <c r="C6" t="n">
-        <v>8538</v>
+        <v>8588</v>
       </c>
       <c r="D6" t="n">
-        <v>2261</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>666</v>
+        <v>480</v>
       </c>
       <c r="C7" t="n">
-        <v>5883</v>
+        <v>6602</v>
       </c>
       <c r="D7" t="n">
-        <v>865</v>
+        <v>881</v>
       </c>
     </row>
     <row r="8">
@@ -3663,10 +3663,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>133</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>2803</v>
+        <v>3506</v>
       </c>
       <c r="D8" t="n">
         <v>442</v>
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>1038</v>
+        <v>1197</v>
       </c>
       <c r="D9" t="n">
-        <v>302</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>340</v>
+        <v>329</v>
       </c>
       <c r="D10" t="n">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="D12" t="n">
         <v>93</v>
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8298</v>
+        <v>5597</v>
       </c>
       <c r="C2" t="n">
-        <v>5937</v>
+        <v>7439</v>
       </c>
       <c r="D2" t="n">
-        <v>13042</v>
+        <v>21483</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3539</v>
+        <v>2508</v>
       </c>
       <c r="C2" t="n">
-        <v>5797</v>
+        <v>10606</v>
       </c>
       <c r="D2" t="n">
-        <v>6581</v>
+        <v>9045</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3978</v>
+        <v>2638</v>
       </c>
       <c r="C3" t="n">
-        <v>5187</v>
+        <v>7575</v>
       </c>
       <c r="D3" t="n">
-        <v>10279</v>
+        <v>11225</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4168</v>
+        <v>3197</v>
       </c>
       <c r="C4" t="n">
-        <v>8084</v>
+        <v>8899</v>
       </c>
       <c r="D4" t="n">
-        <v>9529</v>
+        <v>9923</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1792</v>
+        <v>1335</v>
       </c>
       <c r="C5" t="n">
-        <v>11972</v>
+        <v>11988</v>
       </c>
       <c r="D5" t="n">
-        <v>5046</v>
+        <v>5475</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>615</v>
+        <v>443</v>
       </c>
       <c r="C6" t="n">
-        <v>7355</v>
+        <v>7984</v>
       </c>
       <c r="D6" t="n">
-        <v>1845</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>122</v>
+        <v>86</v>
       </c>
       <c r="C7" t="n">
-        <v>2746</v>
+        <v>3435</v>
       </c>
       <c r="D7" t="n">
-        <v>543</v>
+        <v>536</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
-        <v>1017</v>
+        <v>1173</v>
       </c>
       <c r="D8" t="n">
-        <v>295</v>
+        <v>289</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C9" t="n">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="D9" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="D10" t="n">
-        <v>138</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="D11" t="n">
         <v>91</v>
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="D13" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7723</v>
+        <v>6461</v>
       </c>
       <c r="C2" t="n">
-        <v>5709</v>
+        <v>6933</v>
       </c>
       <c r="D2" t="n">
-        <v>12253</v>
+        <v>23381</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3523</v>
+        <v>2378</v>
       </c>
       <c r="C3" t="n">
-        <v>2992</v>
+        <v>3749</v>
       </c>
       <c r="D3" t="n">
-        <v>2830</v>
+        <v>4248</v>
       </c>
     </row>
     <row r="4">
@@ -4557,7 +4557,7 @@
         <v>193</v>
       </c>
       <c r="C5" t="n">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4571,7 +4571,7 @@
         <v>200</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D6" t="n">
         <v>816</v>
@@ -4585,7 +4585,7 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="D7" t="n">
         <v>538</v>
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11">
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5434</v>
+        <v>6196</v>
       </c>
       <c r="C2" t="n">
-        <v>4410</v>
+        <v>7561</v>
       </c>
       <c r="D2" t="n">
-        <v>12291</v>
+        <v>20919</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4621</v>
+        <v>3628</v>
       </c>
       <c r="C3" t="n">
-        <v>3906</v>
+        <v>4786</v>
       </c>
       <c r="D3" t="n">
-        <v>4204</v>
+        <v>7149</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1565</v>
+        <v>1067</v>
       </c>
       <c r="C4" t="n">
-        <v>1798</v>
+        <v>2241</v>
       </c>
       <c r="D4" t="n">
-        <v>1751</v>
+        <v>2037</v>
       </c>
     </row>
     <row r="5">
@@ -4868,7 +4868,7 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="D5" t="n">
         <v>1198</v>
@@ -4882,7 +4882,7 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="D6" t="n">
         <v>859</v>
@@ -4893,10 +4893,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D7" t="n">
         <v>584</v>
@@ -4907,10 +4907,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D8" t="n">
         <v>439</v>
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="n">
         <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11">
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6277</v>
+        <v>5071</v>
       </c>
       <c r="C2" t="n">
-        <v>4295</v>
+        <v>11153</v>
       </c>
       <c r="D2" t="n">
-        <v>24098</v>
+        <v>21882</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4138</v>
+        <v>4005</v>
       </c>
       <c r="C3" t="n">
-        <v>3618</v>
+        <v>5438</v>
       </c>
       <c r="D3" t="n">
-        <v>5195</v>
+        <v>8837</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2622</v>
+        <v>1996</v>
       </c>
       <c r="C4" t="n">
-        <v>2954</v>
+        <v>3589</v>
       </c>
       <c r="D4" t="n">
-        <v>2168</v>
+        <v>2956</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>702</v>
+        <v>489</v>
       </c>
       <c r="C5" t="n">
-        <v>1078</v>
+        <v>1323</v>
       </c>
       <c r="D5" t="n">
-        <v>1250</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="6">
@@ -5190,10 +5190,10 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="D6" t="n">
         <v>908</v>
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D7" t="n">
-        <v>620</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>454</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>90</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D9" t="n">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11">
@@ -5263,10 +5263,10 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="12">
@@ -5277,10 +5277,10 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D12" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="13">
@@ -5291,10 +5291,10 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D13" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="14">
@@ -5305,7 +5305,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5316,7 +5316,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
@@ -5333,10 +5333,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5375,7 +5375,7 @@
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6115</v>
+        <v>6095</v>
       </c>
       <c r="C2" t="n">
-        <v>3264</v>
+        <v>12184</v>
       </c>
       <c r="D2" t="n">
-        <v>21782</v>
+        <v>18615</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4228</v>
+        <v>3708</v>
       </c>
       <c r="C3" t="n">
-        <v>3452</v>
+        <v>7256</v>
       </c>
       <c r="D3" t="n">
-        <v>7702</v>
+        <v>10197</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2885</v>
+        <v>2504</v>
       </c>
       <c r="C4" t="n">
-        <v>3249</v>
+        <v>4456</v>
       </c>
       <c r="D4" t="n">
-        <v>2654</v>
+        <v>3938</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1368</v>
+        <v>1022</v>
       </c>
       <c r="C5" t="n">
-        <v>2017</v>
+        <v>2470</v>
       </c>
       <c r="D5" t="n">
-        <v>1358</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>364</v>
+        <v>273</v>
       </c>
       <c r="C6" t="n">
-        <v>692</v>
+        <v>810</v>
       </c>
       <c r="D6" t="n">
-        <v>954</v>
+        <v>963</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D7" t="n">
-        <v>655</v>
+        <v>660</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
         <v>378</v>
       </c>
       <c r="D8" t="n">
-        <v>481</v>
+        <v>478</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="D9" t="n">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>341</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="12">
@@ -5588,10 +5588,10 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D12" t="n">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="13">
@@ -5602,10 +5602,10 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D13" t="n">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14">
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15">
@@ -5633,7 +5633,7 @@
         <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5686,7 +5686,7 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8075</v>
+        <v>6474</v>
       </c>
       <c r="C2" t="n">
-        <v>10041</v>
+        <v>12914</v>
       </c>
       <c r="D2" t="n">
-        <v>25228</v>
+        <v>19535</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3791</v>
+        <v>3513</v>
       </c>
       <c r="C3" t="n">
-        <v>2749</v>
+        <v>7972</v>
       </c>
       <c r="D3" t="n">
-        <v>8749</v>
+        <v>10122</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2193</v>
+        <v>1903</v>
       </c>
       <c r="C4" t="n">
-        <v>2728</v>
+        <v>4852</v>
       </c>
       <c r="D4" t="n">
-        <v>3026</v>
+        <v>4325</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1112</v>
+        <v>905</v>
       </c>
       <c r="C5" t="n">
-        <v>1949</v>
+        <v>2556</v>
       </c>
       <c r="D5" t="n">
-        <v>1259</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>413</v>
+        <v>305</v>
       </c>
       <c r="C6" t="n">
-        <v>911</v>
+        <v>1097</v>
       </c>
       <c r="D6" t="n">
-        <v>778</v>
+        <v>807</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="C7" t="n">
-        <v>334</v>
+        <v>363</v>
       </c>
       <c r="D7" t="n">
-        <v>511</v>
+        <v>515</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D9" t="n">
-        <v>269</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>30</v>
       </c>
       <c r="C10" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>232</v>
       </c>
     </row>
     <row r="11">
@@ -5885,10 +5885,10 @@
         <v>21</v>
       </c>
       <c r="C11" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12">
@@ -5902,7 +5902,7 @@
         <v>92</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
         <v>117</v>
@@ -5930,7 +5930,7 @@
         <v>57</v>
       </c>
       <c r="D14" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="15">
@@ -5944,7 +5944,7 @@
         <v>45</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -5997,7 +5997,7 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6449</v>
+        <v>5406</v>
       </c>
       <c r="C2" t="n">
-        <v>9832</v>
+        <v>8888</v>
       </c>
       <c r="D2" t="n">
-        <v>22797</v>
+        <v>21840</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4941</v>
+        <v>4129</v>
       </c>
       <c r="C3" t="n">
-        <v>6091</v>
+        <v>9313</v>
       </c>
       <c r="D3" t="n">
-        <v>10991</v>
+        <v>10958</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2608</v>
+        <v>2367</v>
       </c>
       <c r="C4" t="n">
-        <v>2684</v>
+        <v>6608</v>
       </c>
       <c r="D4" t="n">
-        <v>4142</v>
+        <v>5362</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1485</v>
+        <v>1237</v>
       </c>
       <c r="C5" t="n">
-        <v>2372</v>
+        <v>3825</v>
       </c>
       <c r="D5" t="n">
-        <v>1576</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>712</v>
+        <v>559</v>
       </c>
       <c r="C6" t="n">
-        <v>1497</v>
+        <v>1885</v>
       </c>
       <c r="D6" t="n">
-        <v>851</v>
+        <v>934</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>236</v>
+        <v>178</v>
       </c>
       <c r="C7" t="n">
-        <v>661</v>
+        <v>772</v>
       </c>
       <c r="D7" t="n">
-        <v>558</v>
+        <v>564</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="C8" t="n">
-        <v>281</v>
+        <v>298</v>
       </c>
       <c r="D8" t="n">
-        <v>385</v>
+        <v>380</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D9" t="n">
-        <v>279</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>33</v>
       </c>
       <c r="C10" t="n">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>234</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>23</v>
       </c>
       <c r="C11" t="n">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
         <v>199</v>
@@ -6210,7 +6210,7 @@
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D12" t="n">
         <v>152</v>
@@ -6224,10 +6224,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="14">
@@ -6238,7 +6238,7 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
         <v>98</v>
@@ -6252,7 +6252,7 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D15" t="n">
         <v>79</v>
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6336,10 +6336,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5462</v>
+        <v>5505</v>
       </c>
       <c r="C2" t="n">
-        <v>7654</v>
+        <v>6126</v>
       </c>
       <c r="D2" t="n">
-        <v>18345</v>
+        <v>23562</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4684</v>
+        <v>3905</v>
       </c>
       <c r="C3" t="n">
-        <v>7058</v>
+        <v>7897</v>
       </c>
       <c r="D3" t="n">
-        <v>12088</v>
+        <v>11840</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3260</v>
+        <v>2777</v>
       </c>
       <c r="C4" t="n">
-        <v>4590</v>
+        <v>7887</v>
       </c>
       <c r="D4" t="n">
-        <v>5291</v>
+        <v>6168</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1793</v>
+        <v>1556</v>
       </c>
       <c r="C5" t="n">
-        <v>2496</v>
+        <v>5241</v>
       </c>
       <c r="D5" t="n">
-        <v>2020</v>
+        <v>2556</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1006</v>
+        <v>808</v>
       </c>
       <c r="C6" t="n">
-        <v>1950</v>
+        <v>2869</v>
       </c>
       <c r="D6" t="n">
-        <v>971</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>418</v>
+        <v>317</v>
       </c>
       <c r="C7" t="n">
-        <v>1096</v>
+        <v>1338</v>
       </c>
       <c r="D7" t="n">
-        <v>598</v>
+        <v>623</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="C8" t="n">
-        <v>478</v>
+        <v>527</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>406</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="D9" t="n">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>239</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12">
@@ -6521,10 +6521,10 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -6549,10 +6549,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17">
@@ -6594,7 +6594,7 @@
         <v>37</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -6605,7 +6605,7 @@
         <v>1</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>39</v>
@@ -6619,10 +6619,10 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20">
@@ -6630,7 +6630,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
         <v>29</v>
@@ -6647,10 +6647,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_53_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_53_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6018</v>
+        <v>6215</v>
       </c>
       <c r="C2" t="n">
-        <v>5808</v>
+        <v>7496</v>
       </c>
       <c r="D2" t="n">
-        <v>23474</v>
+        <v>23615</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3800</v>
+        <v>3072</v>
       </c>
       <c r="C3" t="n">
-        <v>6187</v>
+        <v>6337</v>
       </c>
       <c r="D3" t="n">
-        <v>12713</v>
+        <v>15806</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2836</v>
+        <v>2381</v>
       </c>
       <c r="C4" t="n">
-        <v>7652</v>
+        <v>5340</v>
       </c>
       <c r="D4" t="n">
-        <v>6960</v>
+        <v>7558</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1841</v>
+        <v>1588</v>
       </c>
       <c r="C5" t="n">
-        <v>6427</v>
+        <v>4304</v>
       </c>
       <c r="D5" t="n">
-        <v>3043</v>
+        <v>2799</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1044</v>
+        <v>961</v>
       </c>
       <c r="C6" t="n">
-        <v>3927</v>
+        <v>3219</v>
       </c>
       <c r="D6" t="n">
-        <v>1320</v>
+        <v>1146</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C7" t="n">
-        <v>2057</v>
+        <v>1918</v>
       </c>
       <c r="D7" t="n">
-        <v>684</v>
+        <v>649</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="C8" t="n">
-        <v>892</v>
+        <v>876</v>
       </c>
       <c r="D8" t="n">
-        <v>435</v>
+        <v>431</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="D9" t="n">
-        <v>305</v>
+        <v>310</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C10" t="n">
         <v>214</v>
       </c>
       <c r="D10" t="n">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="11">
@@ -909,10 +909,10 @@
         <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D12" t="n">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="13">
@@ -937,10 +937,10 @@
         <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>58</v>
       </c>
       <c r="D15" t="n">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -979,10 +979,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1010,7 +1010,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1021,7 +1021,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1052,7 +1052,7 @@
         <v>97</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6295</v>
+        <v>6402</v>
       </c>
       <c r="C2" t="n">
-        <v>7856</v>
+        <v>7146</v>
       </c>
       <c r="D2" t="n">
-        <v>19355</v>
+        <v>29763</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3868</v>
+        <v>3632</v>
       </c>
       <c r="C3" t="n">
-        <v>5318</v>
+        <v>6040</v>
       </c>
       <c r="D3" t="n">
-        <v>13256</v>
+        <v>15805</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2793</v>
+        <v>2290</v>
       </c>
       <c r="C4" t="n">
-        <v>6817</v>
+        <v>5707</v>
       </c>
       <c r="D4" t="n">
-        <v>7565</v>
+        <v>8674</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1989</v>
+        <v>1706</v>
       </c>
       <c r="C5" t="n">
-        <v>6772</v>
+        <v>4650</v>
       </c>
       <c r="D5" t="n">
-        <v>3552</v>
+        <v>3418</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1246</v>
+        <v>1122</v>
       </c>
       <c r="C6" t="n">
-        <v>4970</v>
+        <v>3677</v>
       </c>
       <c r="D6" t="n">
-        <v>1537</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>630</v>
+        <v>615</v>
       </c>
       <c r="C7" t="n">
-        <v>2824</v>
+        <v>2472</v>
       </c>
       <c r="D7" t="n">
-        <v>770</v>
+        <v>709</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C8" t="n">
-        <v>1371</v>
+        <v>1324</v>
       </c>
       <c r="D8" t="n">
-        <v>460</v>
+        <v>458</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C9" t="n">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="D9" t="n">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C11" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D12" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14">
@@ -1262,10 +1262,10 @@
         <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15">
@@ -1279,7 +1279,7 @@
         <v>63</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1321,7 +1321,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1332,7 +1332,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1363,7 +1363,7 @@
         <v>103</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6857</v>
+        <v>6597</v>
       </c>
       <c r="C2" t="n">
-        <v>13586</v>
+        <v>10295</v>
       </c>
       <c r="D2" t="n">
-        <v>19504</v>
+        <v>30734</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3922</v>
+        <v>3864</v>
       </c>
       <c r="C3" t="n">
-        <v>5612</v>
+        <v>5761</v>
       </c>
       <c r="D3" t="n">
-        <v>13139</v>
+        <v>16468</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2733</v>
+        <v>2405</v>
       </c>
       <c r="C4" t="n">
-        <v>5990</v>
+        <v>5677</v>
       </c>
       <c r="D4" t="n">
-        <v>8154</v>
+        <v>9353</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2045</v>
+        <v>1746</v>
       </c>
       <c r="C5" t="n">
-        <v>6584</v>
+        <v>4955</v>
       </c>
       <c r="D5" t="n">
-        <v>3949</v>
+        <v>4038</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1396</v>
+        <v>1235</v>
       </c>
       <c r="C6" t="n">
-        <v>5636</v>
+        <v>4045</v>
       </c>
       <c r="D6" t="n">
-        <v>1787</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>781</v>
+        <v>733</v>
       </c>
       <c r="C7" t="n">
-        <v>3615</v>
+        <v>2930</v>
       </c>
       <c r="D7" t="n">
-        <v>852</v>
+        <v>787</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="C8" t="n">
-        <v>1898</v>
+        <v>1760</v>
       </c>
       <c r="D8" t="n">
-        <v>494</v>
+        <v>487</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="C9" t="n">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="D9" t="n">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="D10" t="n">
-        <v>249</v>
+        <v>258</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D11" t="n">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>19</v>
       </c>
       <c r="C12" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13">
@@ -1559,10 +1559,10 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C14" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15">
@@ -1587,10 +1587,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -1604,7 +1604,7 @@
         <v>52</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -1615,7 +1615,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -1632,7 +1632,7 @@
         <v>34</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -1643,7 +1643,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>27</v>
@@ -1671,10 +1671,10 @@
         <v>8</v>
       </c>
       <c r="C21" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6395</v>
+        <v>6141</v>
       </c>
       <c r="C2" t="n">
-        <v>9455</v>
+        <v>7000</v>
       </c>
       <c r="D2" t="n">
-        <v>16233</v>
+        <v>25377</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4767</v>
+        <v>4485</v>
       </c>
       <c r="C3" t="n">
-        <v>9388</v>
+        <v>9109</v>
       </c>
       <c r="D3" t="n">
-        <v>14487</v>
+        <v>17892</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1889</v>
+        <v>1613</v>
       </c>
       <c r="C4" t="n">
-        <v>9483</v>
+        <v>7863</v>
       </c>
       <c r="D4" t="n">
-        <v>8052</v>
+        <v>8896</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1289</v>
+        <v>1141</v>
       </c>
       <c r="C5" t="n">
-        <v>5523</v>
+        <v>3964</v>
       </c>
       <c r="D5" t="n">
-        <v>2812</v>
+        <v>2710</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>721</v>
+        <v>677</v>
       </c>
       <c r="C6" t="n">
-        <v>3542</v>
+        <v>2871</v>
       </c>
       <c r="D6" t="n">
-        <v>834</v>
+        <v>771</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="C7" t="n">
-        <v>1860</v>
+        <v>1724</v>
       </c>
       <c r="D7" t="n">
-        <v>484</v>
+        <v>477</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="D8" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="D9" t="n">
-        <v>244</v>
+        <v>252</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="n">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="D10" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12">
@@ -1856,10 +1856,10 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -1884,10 +1884,10 @@
         <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="15">
@@ -1901,7 +1901,7 @@
         <v>50</v>
       </c>
       <c r="D15" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16">
@@ -1912,7 +1912,7 @@
         <v>1</v>
       </c>
       <c r="C16" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D16" t="n">
         <v>50</v>
@@ -1929,7 +1929,7 @@
         <v>33</v>
       </c>
       <c r="D17" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="18">
@@ -1940,7 +1940,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D18" t="n">
         <v>26</v>
@@ -1968,10 +1968,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3924</v>
+        <v>3746</v>
       </c>
       <c r="C2" t="n">
-        <v>4853</v>
+        <v>3533</v>
       </c>
       <c r="D2" t="n">
-        <v>12096</v>
+        <v>18984</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4716</v>
+        <v>4487</v>
       </c>
       <c r="C3" t="n">
-        <v>8558</v>
+        <v>7403</v>
       </c>
       <c r="D3" t="n">
-        <v>14029</v>
+        <v>17879</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2563</v>
+        <v>2329</v>
       </c>
       <c r="C4" t="n">
-        <v>9607</v>
+        <v>8500</v>
       </c>
       <c r="D4" t="n">
-        <v>8811</v>
+        <v>10178</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1434</v>
+        <v>1260</v>
       </c>
       <c r="C5" t="n">
-        <v>7178</v>
+        <v>5681</v>
       </c>
       <c r="D5" t="n">
-        <v>3461</v>
+        <v>3451</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>844</v>
+        <v>795</v>
       </c>
       <c r="C6" t="n">
-        <v>4424</v>
+        <v>3423</v>
       </c>
       <c r="D6" t="n">
-        <v>1019</v>
+        <v>970</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="C7" t="n">
-        <v>2433</v>
+        <v>2161</v>
       </c>
       <c r="D7" t="n">
-        <v>527</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="C8" t="n">
-        <v>1131</v>
+        <v>1112</v>
       </c>
       <c r="D8" t="n">
-        <v>331</v>
+        <v>339</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C9" t="n">
-        <v>396</v>
+        <v>412</v>
       </c>
       <c r="D9" t="n">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="10">
@@ -2139,10 +2139,10 @@
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="D10" t="n">
-        <v>208</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -2153,10 +2153,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D11" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="D12" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -2181,10 +2181,10 @@
         <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>49</v>
       </c>
       <c r="D14" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -2209,7 +2209,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D15" t="n">
         <v>49</v>
@@ -2226,7 +2226,7 @@
         <v>32</v>
       </c>
       <c r="D16" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -2237,7 +2237,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D17" t="n">
         <v>25</v>
@@ -2265,10 +2265,10 @@
         <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4365</v>
+        <v>4545</v>
       </c>
       <c r="C2" t="n">
-        <v>10707</v>
+        <v>5149</v>
       </c>
       <c r="D2" t="n">
-        <v>11347</v>
+        <v>17867</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3697</v>
+        <v>3544</v>
       </c>
       <c r="C3" t="n">
-        <v>6049</v>
+        <v>4952</v>
       </c>
       <c r="D3" t="n">
-        <v>12823</v>
+        <v>16979</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2961</v>
+        <v>2777</v>
       </c>
       <c r="C4" t="n">
-        <v>8903</v>
+        <v>7786</v>
       </c>
       <c r="D4" t="n">
-        <v>9394</v>
+        <v>11125</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1691</v>
+        <v>1518</v>
       </c>
       <c r="C5" t="n">
-        <v>8216</v>
+        <v>6888</v>
       </c>
       <c r="D5" t="n">
-        <v>4177</v>
+        <v>4379</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1001</v>
+        <v>918</v>
       </c>
       <c r="C6" t="n">
-        <v>5572</v>
+        <v>4441</v>
       </c>
       <c r="D6" t="n">
-        <v>1357</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="C7" t="n">
-        <v>3294</v>
+        <v>2725</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>576</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="C8" t="n">
-        <v>1652</v>
+        <v>1543</v>
       </c>
       <c r="D8" t="n">
-        <v>352</v>
+        <v>358</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="C9" t="n">
-        <v>666</v>
+        <v>676</v>
       </c>
       <c r="D9" t="n">
-        <v>264</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="D10" t="n">
-        <v>210</v>
+        <v>216</v>
       </c>
     </row>
     <row r="11">
@@ -2464,10 +2464,10 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="D12" t="n">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="13">
@@ -2492,7 +2492,7 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D13" t="n">
         <v>100</v>
@@ -2509,7 +2509,7 @@
         <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15">
@@ -2520,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D15" t="n">
         <v>48</v>
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -2548,7 +2548,7 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D17" t="n">
         <v>23</v>
@@ -2562,7 +2562,7 @@
         <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D18" t="n">
         <v>13</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2649</v>
+        <v>2678</v>
       </c>
       <c r="C2" t="n">
-        <v>5153</v>
+        <v>2455</v>
       </c>
       <c r="D2" t="n">
-        <v>7919</v>
+        <v>12465</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3714</v>
+        <v>3651</v>
       </c>
       <c r="C3" t="n">
-        <v>7316</v>
+        <v>4867</v>
       </c>
       <c r="D3" t="n">
-        <v>12382</v>
+        <v>16691</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3244</v>
+        <v>3069</v>
       </c>
       <c r="C4" t="n">
-        <v>8753</v>
+        <v>7446</v>
       </c>
       <c r="D4" t="n">
-        <v>9895</v>
+        <v>11868</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1745</v>
+        <v>1597</v>
       </c>
       <c r="C5" t="n">
-        <v>9663</v>
+        <v>8077</v>
       </c>
       <c r="D5" t="n">
-        <v>4386</v>
+        <v>4623</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>804</v>
+        <v>776</v>
       </c>
       <c r="C6" t="n">
-        <v>6491</v>
+        <v>5385</v>
       </c>
       <c r="D6" t="n">
-        <v>1327</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>3263</v>
+        <v>2859</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>577</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C8" t="n">
-        <v>1138</v>
+        <v>1131</v>
       </c>
       <c r="D8" t="n">
-        <v>374</v>
+        <v>378</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="D9" t="n">
-        <v>283</v>
+        <v>289</v>
       </c>
     </row>
     <row r="10">
@@ -2761,10 +2761,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="D10" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C11" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="D11" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D12" t="n">
         <v>98</v>
@@ -2806,7 +2806,7 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -2817,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D14" t="n">
         <v>47</v>
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D15" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16">
@@ -2845,7 +2845,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D16" t="n">
         <v>22</v>
@@ -2859,7 +2859,7 @@
         <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D18" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2755</v>
+        <v>3293</v>
       </c>
       <c r="C2" t="n">
-        <v>6204</v>
+        <v>6606</v>
       </c>
       <c r="D2" t="n">
-        <v>14606</v>
+        <v>13120</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2809</v>
+        <v>2775</v>
       </c>
       <c r="C3" t="n">
-        <v>5672</v>
+        <v>3364</v>
       </c>
       <c r="D3" t="n">
-        <v>10998</v>
+        <v>15154</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3026</v>
+        <v>2886</v>
       </c>
       <c r="C4" t="n">
-        <v>7992</v>
+        <v>6077</v>
       </c>
       <c r="D4" t="n">
-        <v>9976</v>
+        <v>12248</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2068</v>
+        <v>1944</v>
       </c>
       <c r="C5" t="n">
-        <v>9161</v>
+        <v>7701</v>
       </c>
       <c r="D5" t="n">
-        <v>5045</v>
+        <v>5525</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1033</v>
+        <v>995</v>
       </c>
       <c r="C6" t="n">
-        <v>7776</v>
+        <v>6525</v>
       </c>
       <c r="D6" t="n">
-        <v>1733</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="C7" t="n">
-        <v>4527</v>
+        <v>3928</v>
       </c>
       <c r="D7" t="n">
-        <v>665</v>
+        <v>667</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C8" t="n">
-        <v>1920</v>
+        <v>1779</v>
       </c>
       <c r="D8" t="n">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>543</v>
+        <v>568</v>
       </c>
       <c r="D9" t="n">
-        <v>290</v>
+        <v>296</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="D10" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="D11" t="n">
-        <v>134</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13">
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D13" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
@@ -3128,7 +3128,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D14" t="n">
         <v>46</v>
@@ -3142,7 +3142,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D15" t="n">
         <v>33</v>
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1920</v>
+        <v>2152</v>
       </c>
       <c r="C2" t="n">
-        <v>3730</v>
+        <v>3758</v>
       </c>
       <c r="D2" t="n">
-        <v>10675</v>
+        <v>9322</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2448</v>
+        <v>2577</v>
       </c>
       <c r="C3" t="n">
-        <v>5401</v>
+        <v>4251</v>
       </c>
       <c r="D3" t="n">
-        <v>10821</v>
+        <v>14085</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2730</v>
+        <v>2602</v>
       </c>
       <c r="C4" t="n">
-        <v>7088</v>
+        <v>4973</v>
       </c>
       <c r="D4" t="n">
-        <v>9896</v>
+        <v>12383</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2242</v>
+        <v>2128</v>
       </c>
       <c r="C5" t="n">
-        <v>8918</v>
+        <v>7244</v>
       </c>
       <c r="D5" t="n">
-        <v>5509</v>
+        <v>6237</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1189</v>
+        <v>1165</v>
       </c>
       <c r="C6" t="n">
-        <v>8506</v>
+        <v>7161</v>
       </c>
       <c r="D6" t="n">
-        <v>2000</v>
+        <v>2059</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>262</v>
+        <v>279</v>
       </c>
       <c r="C7" t="n">
-        <v>5568</v>
+        <v>4832</v>
       </c>
       <c r="D7" t="n">
-        <v>741</v>
+        <v>759</v>
       </c>
     </row>
     <row r="8">
@@ -3352,10 +3352,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>2478</v>
+        <v>2299</v>
       </c>
       <c r="D8" t="n">
         <v>411</v>
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>604</v>
+        <v>662</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C10" t="n">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="D10" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="D11" t="n">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -3425,10 +3425,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="14">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D14" t="n">
         <v>36</v>
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3434</v>
+        <v>3206</v>
       </c>
       <c r="C2" t="n">
-        <v>17916</v>
+        <v>6058</v>
       </c>
       <c r="D2" t="n">
-        <v>12158</v>
+        <v>8183</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>1914</v>
+        <v>2042</v>
       </c>
       <c r="C3" t="n">
-        <v>4290</v>
+        <v>3638</v>
       </c>
       <c r="D3" t="n">
-        <v>10214</v>
+        <v>12612</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2290</v>
+        <v>2253</v>
       </c>
       <c r="C4" t="n">
-        <v>6260</v>
+        <v>4564</v>
       </c>
       <c r="D4" t="n">
-        <v>9624</v>
+        <v>12251</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2194</v>
+        <v>2110</v>
       </c>
       <c r="C5" t="n">
-        <v>8029</v>
+        <v>6177</v>
       </c>
       <c r="D5" t="n">
-        <v>5931</v>
+        <v>6873</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1423</v>
+        <v>1384</v>
       </c>
       <c r="C6" t="n">
-        <v>8588</v>
+        <v>7132</v>
       </c>
       <c r="D6" t="n">
-        <v>2412</v>
+        <v>2554</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>480</v>
+        <v>494</v>
       </c>
       <c r="C7" t="n">
-        <v>6602</v>
+        <v>5697</v>
       </c>
       <c r="D7" t="n">
-        <v>881</v>
+        <v>896</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="C8" t="n">
-        <v>3506</v>
+        <v>3214</v>
       </c>
       <c r="D8" t="n">
-        <v>442</v>
+        <v>451</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
         <v>1197</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>302</v>
       </c>
     </row>
     <row r="10">
@@ -3691,10 +3691,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C10" t="n">
-        <v>329</v>
+        <v>354</v>
       </c>
       <c r="D10" t="n">
         <v>186</v>
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="12">
@@ -3722,7 +3722,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
         <v>93</v>
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>38</v>
+      </c>
+      <c r="D14" t="n">
         <v>37</v>
-      </c>
-      <c r="D14" t="n">
-        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -3764,7 +3764,7 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D15" t="n">
         <v>18</v>
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5597</v>
+        <v>5668</v>
       </c>
       <c r="C2" t="n">
-        <v>7439</v>
+        <v>5977</v>
       </c>
       <c r="D2" t="n">
-        <v>21483</v>
+        <v>7325</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2508</v>
+        <v>2292</v>
       </c>
       <c r="C2" t="n">
-        <v>10606</v>
+        <v>3440</v>
       </c>
       <c r="D2" t="n">
-        <v>9045</v>
+        <v>6022</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2638</v>
+        <v>2732</v>
       </c>
       <c r="C3" t="n">
-        <v>7575</v>
+        <v>4513</v>
       </c>
       <c r="D3" t="n">
-        <v>11225</v>
+        <v>13454</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3197</v>
+        <v>3100</v>
       </c>
       <c r="C4" t="n">
-        <v>8899</v>
+        <v>6663</v>
       </c>
       <c r="D4" t="n">
-        <v>9923</v>
+        <v>12587</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1335</v>
+        <v>1337</v>
       </c>
       <c r="C5" t="n">
-        <v>11988</v>
+        <v>9623</v>
       </c>
       <c r="D5" t="n">
-        <v>5475</v>
+        <v>6200</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>443</v>
+        <v>456</v>
       </c>
       <c r="C6" t="n">
-        <v>7984</v>
+        <v>6980</v>
       </c>
       <c r="D6" t="n">
-        <v>1918</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>86</v>
+        <v>95</v>
       </c>
       <c r="C7" t="n">
-        <v>3435</v>
+        <v>3149</v>
       </c>
       <c r="D7" t="n">
-        <v>536</v>
+        <v>556</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
         <v>1173</v>
       </c>
       <c r="D8" t="n">
-        <v>289</v>
+        <v>295</v>
       </c>
     </row>
     <row r="9">
@@ -4299,10 +4299,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="D9" t="n">
         <v>182</v>
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="D10" t="n">
-        <v>133</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11">
@@ -4330,7 +4330,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="D11" t="n">
         <v>91</v>
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
+        <v>37</v>
+      </c>
+      <c r="D13" t="n">
         <v>36</v>
-      </c>
-      <c r="D13" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="14">
@@ -4372,7 +4372,7 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
         <v>17</v>
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6461</v>
+        <v>6199</v>
       </c>
       <c r="C2" t="n">
-        <v>6933</v>
+        <v>7275</v>
       </c>
       <c r="D2" t="n">
-        <v>23381</v>
+        <v>18081</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2378</v>
+        <v>2408</v>
       </c>
       <c r="C3" t="n">
-        <v>3749</v>
+        <v>3060</v>
       </c>
       <c r="D3" t="n">
-        <v>4248</v>
+        <v>1869</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>79</v>
       </c>
       <c r="C4" t="n">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D4" t="n">
         <v>1538</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="C5" t="n">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D5" t="n">
         <v>1161</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C6" t="n">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="D6" t="n">
-        <v>816</v>
+        <v>808</v>
       </c>
     </row>
     <row r="7">
@@ -4585,10 +4585,10 @@
         <v>145</v>
       </c>
       <c r="C7" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D7" t="n">
-        <v>538</v>
+        <v>546</v>
       </c>
     </row>
     <row r="8">
@@ -4596,7 +4596,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8" t="n">
         <v>260</v>
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
         <v>205</v>
       </c>
       <c r="D9" t="n">
-        <v>357</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10">
@@ -4630,7 +4630,7 @@
         <v>180</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11">
@@ -4697,7 +4697,7 @@
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D15" t="n">
         <v>118</v>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6196</v>
+        <v>5362</v>
       </c>
       <c r="C2" t="n">
-        <v>7561</v>
+        <v>7844</v>
       </c>
       <c r="D2" t="n">
-        <v>20919</v>
+        <v>21755</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3628</v>
+        <v>3534</v>
       </c>
       <c r="C3" t="n">
-        <v>4786</v>
+        <v>4695</v>
       </c>
       <c r="D3" t="n">
-        <v>7149</v>
+        <v>4455</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1067</v>
+        <v>1079</v>
       </c>
       <c r="C4" t="n">
-        <v>2241</v>
+        <v>1835</v>
       </c>
       <c r="D4" t="n">
-        <v>2037</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>125</v>
       </c>
       <c r="C5" t="n">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D5" t="n">
-        <v>1198</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>185</v>
       </c>
       <c r="C6" t="n">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="D6" t="n">
-        <v>859</v>
+        <v>864</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>584</v>
+        <v>589</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C8" t="n">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C9" t="n">
         <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C10" t="n">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D10" t="n">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11">
@@ -4966,7 +4966,7 @@
         <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
         <v>206</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
         <v>74</v>
@@ -5025,7 +5025,7 @@
         <v>70</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D18" t="n">
         <v>59</v>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5071</v>
+        <v>4380</v>
       </c>
       <c r="C2" t="n">
-        <v>11153</v>
+        <v>7083</v>
       </c>
       <c r="D2" t="n">
-        <v>21882</v>
+        <v>25161</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4005</v>
+        <v>3637</v>
       </c>
       <c r="C3" t="n">
-        <v>5438</v>
+        <v>5550</v>
       </c>
       <c r="D3" t="n">
-        <v>8837</v>
+        <v>6902</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1996</v>
+        <v>1962</v>
       </c>
       <c r="C4" t="n">
-        <v>3589</v>
+        <v>3416</v>
       </c>
       <c r="D4" t="n">
-        <v>2956</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="C5" t="n">
-        <v>1323</v>
+        <v>1099</v>
       </c>
       <c r="D5" t="n">
-        <v>1303</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="6">
@@ -5193,10 +5193,10 @@
         <v>148</v>
       </c>
       <c r="C6" t="n">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="D6" t="n">
-        <v>908</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C7" t="n">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="D7" t="n">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8">
@@ -5221,10 +5221,10 @@
         <v>125</v>
       </c>
       <c r="C8" t="n">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="D8" t="n">
-        <v>454</v>
+        <v>462</v>
       </c>
     </row>
     <row r="9">
@@ -5235,10 +5235,10 @@
         <v>90</v>
       </c>
       <c r="C9" t="n">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D9" t="n">
-        <v>374</v>
+        <v>372</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C10" t="n">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D10" t="n">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5263,10 +5263,10 @@
         <v>47</v>
       </c>
       <c r="C11" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D11" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="12">
@@ -5277,7 +5277,7 @@
         <v>31</v>
       </c>
       <c r="C12" t="n">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D12" t="n">
         <v>213</v>
@@ -5291,7 +5291,7 @@
         <v>21</v>
       </c>
       <c r="C13" t="n">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D13" t="n">
         <v>173</v>
@@ -5305,7 +5305,7 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D14" t="n">
         <v>148</v>
@@ -5316,7 +5316,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>77</v>
@@ -5333,10 +5333,10 @@
         <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17">
@@ -5350,7 +5350,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5406,7 +5406,7 @@
         <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6095</v>
+        <v>4395</v>
       </c>
       <c r="C2" t="n">
-        <v>12184</v>
+        <v>6181</v>
       </c>
       <c r="D2" t="n">
-        <v>18615</v>
+        <v>27494</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3708</v>
+        <v>3289</v>
       </c>
       <c r="C3" t="n">
-        <v>7256</v>
+        <v>5517</v>
       </c>
       <c r="D3" t="n">
-        <v>10197</v>
+        <v>9191</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2504</v>
+        <v>2375</v>
       </c>
       <c r="C4" t="n">
-        <v>4456</v>
+        <v>4492</v>
       </c>
       <c r="D4" t="n">
-        <v>3938</v>
+        <v>2885</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1022</v>
+        <v>1007</v>
       </c>
       <c r="C5" t="n">
-        <v>2470</v>
+        <v>2266</v>
       </c>
       <c r="D5" t="n">
-        <v>1536</v>
+        <v>1306</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="C6" t="n">
-        <v>810</v>
+        <v>703</v>
       </c>
       <c r="D6" t="n">
-        <v>963</v>
+        <v>948</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C7" t="n">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D7" t="n">
-        <v>660</v>
+        <v>659</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C8" t="n">
         <v>378</v>
       </c>
       <c r="D8" t="n">
-        <v>478</v>
+        <v>484</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C9" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D9" t="n">
-        <v>382</v>
+        <v>378</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C10" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="D10" t="n">
-        <v>341</v>
+        <v>346</v>
       </c>
     </row>
     <row r="11">
@@ -5574,10 +5574,10 @@
         <v>50</v>
       </c>
       <c r="C11" t="n">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D11" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12">
@@ -5588,7 +5588,7 @@
         <v>34</v>
       </c>
       <c r="C12" t="n">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D12" t="n">
         <v>217</v>
@@ -5602,7 +5602,7 @@
         <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D13" t="n">
         <v>176</v>
@@ -5616,10 +5616,10 @@
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D14" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -5633,7 +5633,7 @@
         <v>81</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16">
@@ -5644,10 +5644,10 @@
         <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D16" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -5661,7 +5661,7 @@
         <v>68</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="18">
@@ -5686,7 +5686,7 @@
         <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D19" t="n">
         <v>41</v>
@@ -5717,7 +5717,7 @@
         <v>137</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6474</v>
+        <v>5084</v>
       </c>
       <c r="C2" t="n">
-        <v>12914</v>
+        <v>7176</v>
       </c>
       <c r="D2" t="n">
-        <v>19535</v>
+        <v>32843</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3513</v>
+        <v>2787</v>
       </c>
       <c r="C3" t="n">
-        <v>7972</v>
+        <v>4797</v>
       </c>
       <c r="D3" t="n">
-        <v>10122</v>
+        <v>10655</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1903</v>
+        <v>1747</v>
       </c>
       <c r="C4" t="n">
-        <v>4852</v>
+        <v>4142</v>
       </c>
       <c r="D4" t="n">
-        <v>4325</v>
+        <v>3445</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>905</v>
+        <v>884</v>
       </c>
       <c r="C5" t="n">
-        <v>2556</v>
+        <v>2484</v>
       </c>
       <c r="D5" t="n">
-        <v>1530</v>
+        <v>1236</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C6" t="n">
-        <v>1097</v>
+        <v>1004</v>
       </c>
       <c r="D6" t="n">
-        <v>807</v>
+        <v>768</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C7" t="n">
-        <v>363</v>
+        <v>333</v>
       </c>
       <c r="D7" t="n">
-        <v>515</v>
+        <v>513</v>
       </c>
     </row>
     <row r="8">
@@ -5846,7 +5846,7 @@
         <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>44</v>
       </c>
       <c r="C9" t="n">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="D9" t="n">
-        <v>274</v>
+        <v>270</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C10" t="n">
         <v>150</v>
       </c>
       <c r="D10" t="n">
-        <v>232</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>114</v>
       </c>
       <c r="D11" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12">
@@ -5899,10 +5899,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D12" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13">
@@ -5913,7 +5913,7 @@
         <v>9</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D13" t="n">
         <v>117</v>
@@ -5941,10 +5941,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D15" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>38</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +5969,7 @@
         <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="n">
         <v>50</v>
@@ -5980,10 +5980,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="n">
         <v>38</v>
@@ -5997,7 +5997,7 @@
         <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
         <v>26</v>
@@ -6011,7 +6011,7 @@
         <v>2</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>15</v>
@@ -6028,7 +6028,7 @@
         <v>75</v>
       </c>
       <c r="D21" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5406</v>
+        <v>5038</v>
       </c>
       <c r="C2" t="n">
-        <v>8888</v>
+        <v>8449</v>
       </c>
       <c r="D2" t="n">
-        <v>21840</v>
+        <v>28409</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4129</v>
+        <v>3271</v>
       </c>
       <c r="C3" t="n">
-        <v>9313</v>
+        <v>5320</v>
       </c>
       <c r="D3" t="n">
-        <v>10958</v>
+        <v>13598</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2367</v>
+        <v>1987</v>
       </c>
       <c r="C4" t="n">
-        <v>6608</v>
+        <v>4451</v>
       </c>
       <c r="D4" t="n">
-        <v>5362</v>
+        <v>4760</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1237</v>
+        <v>1175</v>
       </c>
       <c r="C5" t="n">
-        <v>3825</v>
+        <v>3403</v>
       </c>
       <c r="D5" t="n">
-        <v>2005</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>559</v>
+        <v>545</v>
       </c>
       <c r="C6" t="n">
-        <v>1885</v>
+        <v>1820</v>
       </c>
       <c r="D6" t="n">
-        <v>934</v>
+        <v>846</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C7" t="n">
-        <v>772</v>
+        <v>714</v>
       </c>
       <c r="D7" t="n">
-        <v>564</v>
+        <v>550</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C8" t="n">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="D8" t="n">
-        <v>380</v>
+        <v>388</v>
       </c>
     </row>
     <row r="9">
@@ -6168,10 +6168,10 @@
         <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D9" t="n">
-        <v>286</v>
+        <v>281</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C10" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="11">
@@ -6224,10 +6224,10 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D13" t="n">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="14">
@@ -6235,7 +6235,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
         <v>63</v>
@@ -6280,7 +6280,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
         <v>51</v>
@@ -6297,7 +6297,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6322,7 +6322,7 @@
         <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6339,7 +6339,7 @@
         <v>83</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5505</v>
+        <v>4115</v>
       </c>
       <c r="C2" t="n">
-        <v>6126</v>
+        <v>8455</v>
       </c>
       <c r="D2" t="n">
-        <v>23562</v>
+        <v>27833</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3905</v>
+        <v>3396</v>
       </c>
       <c r="C3" t="n">
-        <v>7897</v>
+        <v>6081</v>
       </c>
       <c r="D3" t="n">
-        <v>11840</v>
+        <v>14988</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2777</v>
+        <v>2262</v>
       </c>
       <c r="C4" t="n">
-        <v>7887</v>
+        <v>4850</v>
       </c>
       <c r="D4" t="n">
-        <v>6168</v>
+        <v>6312</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1556</v>
+        <v>1381</v>
       </c>
       <c r="C5" t="n">
-        <v>5241</v>
+        <v>3905</v>
       </c>
       <c r="D5" t="n">
-        <v>2556</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>808</v>
+        <v>781</v>
       </c>
       <c r="C6" t="n">
-        <v>2869</v>
+        <v>2617</v>
       </c>
       <c r="D6" t="n">
-        <v>1097</v>
+        <v>979</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C7" t="n">
-        <v>1338</v>
+        <v>1299</v>
       </c>
       <c r="D7" t="n">
-        <v>623</v>
+        <v>591</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C8" t="n">
-        <v>527</v>
+        <v>502</v>
       </c>
       <c r="D8" t="n">
-        <v>406</v>
+        <v>412</v>
       </c>
     </row>
     <row r="9">
@@ -6479,7 +6479,7 @@
         <v>51</v>
       </c>
       <c r="C9" t="n">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="D9" t="n">
         <v>295</v>
@@ -6493,10 +6493,10 @@
         <v>36</v>
       </c>
       <c r="C10" t="n">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="D10" t="n">
-        <v>239</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="12">
@@ -6521,7 +6521,7 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D12" t="n">
         <v>157</v>
@@ -6535,7 +6535,7 @@
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D13" t="n">
         <v>121</v>
@@ -6552,7 +6552,7 @@
         <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -6563,10 +6563,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D15" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>43</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17">
@@ -6591,7 +6591,7 @@
         <v>2</v>
       </c>
       <c r="C17" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D17" t="n">
         <v>52</v>
@@ -6608,7 +6608,7 @@
         <v>33</v>
       </c>
       <c r="D18" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="19">
@@ -6619,10 +6619,10 @@
         <v>1</v>
       </c>
       <c r="C19" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -6630,10 +6630,10 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C20" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D20" t="n">
         <v>16</v>
@@ -6650,7 +6650,7 @@
         <v>90</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_population_iteration_53_growth_param_0.5.xlsx
+++ b/output/yearly_population_iteration_53_growth_param_0.5.xlsx
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6215</v>
+        <v>850</v>
       </c>
       <c r="C2" t="n">
-        <v>7496</v>
+        <v>2562</v>
       </c>
       <c r="D2" t="n">
-        <v>23615</v>
+        <v>10326</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3072</v>
+        <v>1543</v>
       </c>
       <c r="C3" t="n">
-        <v>6337</v>
+        <v>7335</v>
       </c>
       <c r="D3" t="n">
-        <v>15806</v>
+        <v>11074</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2381</v>
+        <v>1157</v>
       </c>
       <c r="C4" t="n">
-        <v>5340</v>
+        <v>9349</v>
       </c>
       <c r="D4" t="n">
-        <v>7558</v>
+        <v>6105</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1588</v>
+        <v>596</v>
       </c>
       <c r="C5" t="n">
-        <v>4304</v>
+        <v>5868</v>
       </c>
       <c r="D5" t="n">
-        <v>2799</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>961</v>
+        <v>232</v>
       </c>
       <c r="C6" t="n">
-        <v>3219</v>
+        <v>2453</v>
       </c>
       <c r="D6" t="n">
-        <v>1146</v>
+        <v>760</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>470</v>
+        <v>93</v>
       </c>
       <c r="C7" t="n">
-        <v>1918</v>
+        <v>868</v>
       </c>
       <c r="D7" t="n">
-        <v>649</v>
+        <v>484</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>178</v>
+        <v>73</v>
       </c>
       <c r="C8" t="n">
-        <v>876</v>
+        <v>365</v>
       </c>
       <c r="D8" t="n">
-        <v>431</v>
+        <v>373</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="C9" t="n">
-        <v>358</v>
+        <v>279</v>
       </c>
       <c r="D9" t="n">
-        <v>310</v>
+        <v>317</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D10" t="n">
-        <v>246</v>
+        <v>264</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="D11" t="n">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>127</v>
+        <v>110</v>
       </c>
       <c r="D12" t="n">
-        <v>161</v>
+        <v>174</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C13" t="n">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="D13" t="n">
-        <v>123</v>
+        <v>139</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>101</v>
+        <v>88</v>
       </c>
     </row>
     <row r="15">
@@ -965,10 +965,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C16" t="n">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
+        <v>52</v>
+      </c>
+      <c r="D17" t="n">
         <v>38</v>
-      </c>
-      <c r="D17" t="n">
-        <v>52</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>21</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>140</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6402</v>
+        <v>1418</v>
       </c>
       <c r="C2" t="n">
-        <v>7146</v>
+        <v>14528</v>
       </c>
       <c r="D2" t="n">
-        <v>29763</v>
+        <v>11775</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3632</v>
+        <v>1042</v>
       </c>
       <c r="C3" t="n">
-        <v>6040</v>
+        <v>4266</v>
       </c>
       <c r="D3" t="n">
-        <v>15805</v>
+        <v>10180</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2290</v>
+        <v>1153</v>
       </c>
       <c r="C4" t="n">
-        <v>5707</v>
+        <v>8161</v>
       </c>
       <c r="D4" t="n">
-        <v>8674</v>
+        <v>6825</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1706</v>
+        <v>759</v>
       </c>
       <c r="C5" t="n">
-        <v>4650</v>
+        <v>7517</v>
       </c>
       <c r="D5" t="n">
-        <v>3418</v>
+        <v>2723</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1122</v>
+        <v>351</v>
       </c>
       <c r="C6" t="n">
-        <v>3677</v>
+        <v>4123</v>
       </c>
       <c r="D6" t="n">
-        <v>1384</v>
+        <v>967</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>615</v>
+        <v>135</v>
       </c>
       <c r="C7" t="n">
-        <v>2472</v>
+        <v>1621</v>
       </c>
       <c r="D7" t="n">
-        <v>709</v>
+        <v>527</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>263</v>
+        <v>76</v>
       </c>
       <c r="C8" t="n">
-        <v>1324</v>
+        <v>590</v>
       </c>
       <c r="D8" t="n">
-        <v>458</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -1189,10 +1189,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>98</v>
+        <v>56</v>
       </c>
       <c r="C9" t="n">
-        <v>567</v>
+        <v>319</v>
       </c>
       <c r="D9" t="n">
         <v>320</v>
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="C10" t="n">
-        <v>271</v>
+        <v>239</v>
       </c>
       <c r="D10" t="n">
-        <v>252</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
-        <v>205</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="D12" t="n">
-        <v>164</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C13" t="n">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="D13" t="n">
-        <v>125</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>102</v>
+        <v>93</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>4</v>
       </c>
       <c r="C15" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>3</v>
       </c>
       <c r="C16" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C17" t="n">
-        <v>39</v>
+        <v>56</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>94</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6597</v>
+        <v>760</v>
       </c>
       <c r="C2" t="n">
-        <v>10295</v>
+        <v>6178</v>
       </c>
       <c r="D2" t="n">
-        <v>30734</v>
+        <v>8055</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3864</v>
+        <v>1102</v>
       </c>
       <c r="C3" t="n">
-        <v>5761</v>
+        <v>7960</v>
       </c>
       <c r="D3" t="n">
-        <v>16468</v>
+        <v>10110</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2405</v>
+        <v>1254</v>
       </c>
       <c r="C4" t="n">
-        <v>5677</v>
+        <v>7316</v>
       </c>
       <c r="D4" t="n">
-        <v>9353</v>
+        <v>7299</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1746</v>
+        <v>757</v>
       </c>
       <c r="C5" t="n">
-        <v>4955</v>
+        <v>8650</v>
       </c>
       <c r="D5" t="n">
-        <v>4038</v>
+        <v>3026</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1235</v>
+        <v>280</v>
       </c>
       <c r="C6" t="n">
-        <v>4045</v>
+        <v>5166</v>
       </c>
       <c r="D6" t="n">
-        <v>1658</v>
+        <v>981</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>733</v>
+        <v>70</v>
       </c>
       <c r="C7" t="n">
-        <v>2930</v>
+        <v>1519</v>
       </c>
       <c r="D7" t="n">
-        <v>787</v>
+        <v>555</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>352</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1760</v>
+        <v>514</v>
       </c>
       <c r="D8" t="n">
-        <v>487</v>
+        <v>434</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>140</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>856</v>
+        <v>234</v>
       </c>
       <c r="D9" t="n">
-        <v>331</v>
+        <v>361</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>57</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>375</v>
+        <v>184</v>
       </c>
       <c r="D10" t="n">
-        <v>258</v>
+        <v>211</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="C11" t="n">
-        <v>211</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>206</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C12" t="n">
-        <v>155</v>
+        <v>85</v>
       </c>
       <c r="D12" t="n">
-        <v>167</v>
+        <v>139</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>63</v>
       </c>
       <c r="D14" t="n">
-        <v>103</v>
+        <v>68</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C16" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
-        <v>41</v>
+        <v>92</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>16</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34</v>
+        <v>74</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6141</v>
+        <v>531</v>
       </c>
       <c r="C2" t="n">
-        <v>7000</v>
+        <v>7909</v>
       </c>
       <c r="D2" t="n">
-        <v>25377</v>
+        <v>7179</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4485</v>
+        <v>808</v>
       </c>
       <c r="C3" t="n">
-        <v>9109</v>
+        <v>6184</v>
       </c>
       <c r="D3" t="n">
-        <v>17892</v>
+        <v>9118</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1613</v>
+        <v>1055</v>
       </c>
       <c r="C4" t="n">
-        <v>7863</v>
+        <v>7567</v>
       </c>
       <c r="D4" t="n">
-        <v>8896</v>
+        <v>7562</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1141</v>
+        <v>871</v>
       </c>
       <c r="C5" t="n">
-        <v>3964</v>
+        <v>7899</v>
       </c>
       <c r="D5" t="n">
-        <v>2710</v>
+        <v>3660</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>677</v>
+        <v>425</v>
       </c>
       <c r="C6" t="n">
-        <v>2871</v>
+        <v>6821</v>
       </c>
       <c r="D6" t="n">
-        <v>771</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>325</v>
+        <v>126</v>
       </c>
       <c r="C7" t="n">
-        <v>1724</v>
+        <v>3120</v>
       </c>
       <c r="D7" t="n">
-        <v>477</v>
+        <v>613</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>129</v>
+        <v>54</v>
       </c>
       <c r="C8" t="n">
-        <v>838</v>
+        <v>917</v>
       </c>
       <c r="D8" t="n">
-        <v>324</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>367</v>
+        <v>339</v>
       </c>
       <c r="D9" t="n">
-        <v>252</v>
+        <v>368</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
         <v>206</v>
       </c>
       <c r="D10" t="n">
-        <v>201</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="D11" t="n">
-        <v>163</v>
+        <v>178</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C12" t="n">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="D12" t="n">
-        <v>123</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C13" t="n">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C14" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D14" t="n">
-        <v>77</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>2</v>
       </c>
       <c r="C15" t="n">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>63</v>
+        <v>49</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="D16" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33</v>
+        <v>99</v>
       </c>
       <c r="D17" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="D18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>109</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3746</v>
+        <v>341</v>
       </c>
       <c r="C2" t="n">
-        <v>3533</v>
+        <v>4541</v>
       </c>
       <c r="D2" t="n">
-        <v>18984</v>
+        <v>5470</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4487</v>
+        <v>620</v>
       </c>
       <c r="C3" t="n">
-        <v>7403</v>
+        <v>6246</v>
       </c>
       <c r="D3" t="n">
-        <v>17879</v>
+        <v>8359</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2329</v>
+        <v>899</v>
       </c>
       <c r="C4" t="n">
-        <v>8500</v>
+        <v>7003</v>
       </c>
       <c r="D4" t="n">
-        <v>10178</v>
+        <v>7628</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1260</v>
+        <v>909</v>
       </c>
       <c r="C5" t="n">
-        <v>5681</v>
+        <v>7904</v>
       </c>
       <c r="D5" t="n">
-        <v>3451</v>
+        <v>4105</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>795</v>
+        <v>515</v>
       </c>
       <c r="C6" t="n">
-        <v>3423</v>
+        <v>7542</v>
       </c>
       <c r="D6" t="n">
-        <v>970</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>307</v>
+        <v>134</v>
       </c>
       <c r="C7" t="n">
-        <v>2161</v>
+        <v>4348</v>
       </c>
       <c r="D7" t="n">
-        <v>520</v>
+        <v>684</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>108</v>
+        <v>51</v>
       </c>
       <c r="C8" t="n">
-        <v>1112</v>
+        <v>1414</v>
       </c>
       <c r="D8" t="n">
-        <v>339</v>
+        <v>471</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>412</v>
+        <v>435</v>
       </c>
       <c r="D9" t="n">
-        <v>260</v>
+        <v>369</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="D10" t="n">
-        <v>211</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>151</v>
       </c>
       <c r="D11" t="n">
-        <v>167</v>
+        <v>185</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="D12" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="D13" t="n">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D14" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>39</v>
+        <v>88</v>
       </c>
       <c r="D15" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>97</v>
       </c>
       <c r="D16" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>106</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4545</v>
+        <v>889</v>
       </c>
       <c r="C2" t="n">
-        <v>5149</v>
+        <v>11091</v>
       </c>
       <c r="D2" t="n">
-        <v>17867</v>
+        <v>8787</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3544</v>
+        <v>431</v>
       </c>
       <c r="C3" t="n">
-        <v>4952</v>
+        <v>4898</v>
       </c>
       <c r="D3" t="n">
-        <v>16979</v>
+        <v>7440</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2777</v>
+        <v>688</v>
       </c>
       <c r="C4" t="n">
-        <v>7786</v>
+        <v>6508</v>
       </c>
       <c r="D4" t="n">
-        <v>11125</v>
+        <v>7508</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1518</v>
+        <v>837</v>
       </c>
       <c r="C5" t="n">
-        <v>6888</v>
+        <v>7341</v>
       </c>
       <c r="D5" t="n">
-        <v>4379</v>
+        <v>4448</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>918</v>
+        <v>613</v>
       </c>
       <c r="C6" t="n">
-        <v>4441</v>
+        <v>7699</v>
       </c>
       <c r="D6" t="n">
-        <v>1314</v>
+        <v>1856</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>436</v>
+        <v>236</v>
       </c>
       <c r="C7" t="n">
-        <v>2725</v>
+        <v>5629</v>
       </c>
       <c r="D7" t="n">
-        <v>576</v>
+        <v>789</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>158</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>1543</v>
+        <v>2548</v>
       </c>
       <c r="D8" t="n">
-        <v>358</v>
+        <v>497</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="C9" t="n">
-        <v>676</v>
+        <v>784</v>
       </c>
       <c r="D9" t="n">
-        <v>266</v>
+        <v>376</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C10" t="n">
         <v>294</v>
       </c>
       <c r="D10" t="n">
-        <v>216</v>
+        <v>242</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="D11" t="n">
-        <v>170</v>
+        <v>188</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="C12" t="n">
         <v>118</v>
       </c>
       <c r="D12" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="D13" t="n">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C14" t="n">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="D14" t="n">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C15" t="n">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="D15" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>35</v>
+        <v>96</v>
       </c>
       <c r="D16" t="n">
-        <v>35</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2678</v>
+        <v>611</v>
       </c>
       <c r="C2" t="n">
-        <v>2455</v>
+        <v>6033</v>
       </c>
       <c r="D2" t="n">
-        <v>12465</v>
+        <v>6396</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3651</v>
+        <v>671</v>
       </c>
       <c r="C3" t="n">
-        <v>4867</v>
+        <v>6883</v>
       </c>
       <c r="D3" t="n">
-        <v>16691</v>
+        <v>8207</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3069</v>
+        <v>1115</v>
       </c>
       <c r="C4" t="n">
-        <v>7446</v>
+        <v>8949</v>
       </c>
       <c r="D4" t="n">
-        <v>11868</v>
+        <v>7800</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1597</v>
+        <v>605</v>
       </c>
       <c r="C5" t="n">
-        <v>8077</v>
+        <v>10813</v>
       </c>
       <c r="D5" t="n">
-        <v>4623</v>
+        <v>4136</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>776</v>
+        <v>218</v>
       </c>
       <c r="C6" t="n">
-        <v>5385</v>
+        <v>7251</v>
       </c>
       <c r="D6" t="n">
-        <v>1287</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>64</v>
       </c>
       <c r="C7" t="n">
-        <v>2859</v>
+        <v>2497</v>
       </c>
       <c r="D7" t="n">
-        <v>577</v>
+        <v>595</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
-        <v>1131</v>
+        <v>768</v>
       </c>
       <c r="D8" t="n">
-        <v>378</v>
+        <v>368</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
         <v>288</v>
       </c>
       <c r="D9" t="n">
-        <v>289</v>
+        <v>237</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="C10" t="n">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="D10" t="n">
-        <v>166</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C11" t="n">
         <v>115</v>
       </c>
       <c r="D11" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="D12" t="n">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>54</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C14" t="n">
-        <v>42</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>94</v>
       </c>
       <c r="D15" t="n">
-        <v>34</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3293</v>
+        <v>305</v>
       </c>
       <c r="C2" t="n">
-        <v>6606</v>
+        <v>3241</v>
       </c>
       <c r="D2" t="n">
-        <v>13120</v>
+        <v>4662</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2775</v>
+        <v>548</v>
       </c>
       <c r="C3" t="n">
-        <v>3364</v>
+        <v>5727</v>
       </c>
       <c r="D3" t="n">
-        <v>15154</v>
+        <v>7384</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2886</v>
+        <v>763</v>
       </c>
       <c r="C4" t="n">
-        <v>6077</v>
+        <v>7516</v>
       </c>
       <c r="D4" t="n">
-        <v>12248</v>
+        <v>7318</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1944</v>
+        <v>574</v>
       </c>
       <c r="C5" t="n">
-        <v>7701</v>
+        <v>8743</v>
       </c>
       <c r="D5" t="n">
-        <v>5525</v>
+        <v>4124</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>995</v>
+        <v>210</v>
       </c>
       <c r="C6" t="n">
-        <v>6525</v>
+        <v>7215</v>
       </c>
       <c r="D6" t="n">
-        <v>1718</v>
+        <v>1645</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>299</v>
+        <v>51</v>
       </c>
       <c r="C7" t="n">
-        <v>3928</v>
+        <v>3188</v>
       </c>
       <c r="D7" t="n">
-        <v>667</v>
+        <v>576</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>66</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>1779</v>
+        <v>897</v>
       </c>
       <c r="D8" t="n">
-        <v>399</v>
+        <v>319</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C9" t="n">
-        <v>568</v>
+        <v>273</v>
       </c>
       <c r="D9" t="n">
-        <v>296</v>
+        <v>186</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>218</v>
+        <v>122</v>
       </c>
       <c r="D10" t="n">
-        <v>174</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>135</v>
+        <v>74</v>
       </c>
       <c r="D11" t="n">
-        <v>136</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>80</v>
+        <v>53</v>
       </c>
       <c r="D12" t="n">
-        <v>99</v>
+        <v>61</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>61</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="D14" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2152</v>
+        <v>143</v>
       </c>
       <c r="C2" t="n">
-        <v>3758</v>
+        <v>7056</v>
       </c>
       <c r="D2" t="n">
-        <v>9322</v>
+        <v>11425</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2577</v>
+        <v>366</v>
       </c>
       <c r="C3" t="n">
-        <v>4251</v>
+        <v>3896</v>
       </c>
       <c r="D3" t="n">
-        <v>14085</v>
+        <v>6450</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2602</v>
+        <v>578</v>
       </c>
       <c r="C4" t="n">
-        <v>4973</v>
+        <v>6397</v>
       </c>
       <c r="D4" t="n">
-        <v>12383</v>
+        <v>7107</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2128</v>
+        <v>598</v>
       </c>
       <c r="C5" t="n">
-        <v>7244</v>
+        <v>7925</v>
       </c>
       <c r="D5" t="n">
-        <v>6237</v>
+        <v>4550</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1165</v>
+        <v>337</v>
       </c>
       <c r="C6" t="n">
-        <v>7161</v>
+        <v>7970</v>
       </c>
       <c r="D6" t="n">
-        <v>2059</v>
+        <v>2027</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>279</v>
+        <v>104</v>
       </c>
       <c r="C7" t="n">
-        <v>4832</v>
+        <v>5151</v>
       </c>
       <c r="D7" t="n">
-        <v>759</v>
+        <v>737</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>54</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>2299</v>
+        <v>1929</v>
       </c>
       <c r="D8" t="n">
-        <v>411</v>
+        <v>353</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C9" t="n">
-        <v>662</v>
+        <v>547</v>
       </c>
       <c r="D9" t="n">
-        <v>294</v>
+        <v>202</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>224</v>
+        <v>182</v>
       </c>
       <c r="D10" t="n">
-        <v>178</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>92</v>
       </c>
       <c r="D11" t="n">
-        <v>137</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="D12" t="n">
-        <v>92</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D13" t="n">
-        <v>62</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="D14" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3206</v>
+        <v>451</v>
       </c>
       <c r="C2" t="n">
-        <v>6058</v>
+        <v>19274</v>
       </c>
       <c r="D2" t="n">
-        <v>8183</v>
+        <v>12115</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2042</v>
+        <v>230</v>
       </c>
       <c r="C3" t="n">
-        <v>3638</v>
+        <v>4711</v>
       </c>
       <c r="D3" t="n">
-        <v>12612</v>
+        <v>6693</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2253</v>
+        <v>421</v>
       </c>
       <c r="C4" t="n">
-        <v>4564</v>
+        <v>5039</v>
       </c>
       <c r="D4" t="n">
-        <v>12251</v>
+        <v>6715</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2110</v>
+        <v>538</v>
       </c>
       <c r="C5" t="n">
-        <v>6177</v>
+        <v>7041</v>
       </c>
       <c r="D5" t="n">
-        <v>6873</v>
+        <v>4828</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>1384</v>
+        <v>411</v>
       </c>
       <c r="C6" t="n">
-        <v>7132</v>
+        <v>7793</v>
       </c>
       <c r="D6" t="n">
-        <v>2554</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>494</v>
+        <v>177</v>
       </c>
       <c r="C7" t="n">
-        <v>5697</v>
+        <v>6419</v>
       </c>
       <c r="D7" t="n">
-        <v>896</v>
+        <v>911</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>103</v>
+        <v>48</v>
       </c>
       <c r="C8" t="n">
-        <v>3214</v>
+        <v>3317</v>
       </c>
       <c r="D8" t="n">
-        <v>451</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C9" t="n">
-        <v>1197</v>
+        <v>1115</v>
       </c>
       <c r="D9" t="n">
-        <v>302</v>
+        <v>220</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="C10" t="n">
-        <v>354</v>
+        <v>325</v>
       </c>
       <c r="D10" t="n">
-        <v>186</v>
+        <v>149</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="D11" t="n">
-        <v>140</v>
+        <v>106</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="D12" t="n">
-        <v>93</v>
+        <v>67</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="D13" t="n">
-        <v>64</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>68</v>
+        <v>2</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5668</v>
+        <v>2368</v>
       </c>
       <c r="C2" t="n">
-        <v>5977</v>
+        <v>14610</v>
       </c>
       <c r="D2" t="n">
-        <v>7325</v>
+        <v>21860</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>843</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C4" t="n">
-        <v>313</v>
+        <v>344</v>
       </c>
       <c r="D4" t="n">
-        <v>1805</v>
+        <v>1906</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>249</v>
+        <v>314</v>
       </c>
       <c r="C5" t="n">
-        <v>515</v>
+        <v>586</v>
       </c>
       <c r="D5" t="n">
-        <v>1038</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>182</v>
+        <v>255</v>
       </c>
       <c r="C6" t="n">
-        <v>395</v>
+        <v>488</v>
       </c>
       <c r="D6" t="n">
-        <v>777</v>
+        <v>898</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>129</v>
+        <v>202</v>
       </c>
       <c r="C7" t="n">
-        <v>293</v>
+        <v>388</v>
       </c>
       <c r="D7" t="n">
-        <v>496</v>
+        <v>596</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>99</v>
+        <v>171</v>
       </c>
       <c r="C8" t="n">
-        <v>222</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>420</v>
+        <v>531</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>75</v>
+        <v>136</v>
       </c>
       <c r="C9" t="n">
-        <v>187</v>
+        <v>277</v>
       </c>
       <c r="D9" t="n">
-        <v>349</v>
+        <v>445</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>105</v>
       </c>
       <c r="C10" t="n">
-        <v>173</v>
+        <v>265</v>
       </c>
       <c r="D10" t="n">
-        <v>362</v>
+        <v>485</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>34</v>
+        <v>71</v>
       </c>
       <c r="C11" t="n">
-        <v>137</v>
+        <v>215</v>
       </c>
       <c r="D11" t="n">
-        <v>245</v>
+        <v>327</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C12" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="D12" t="n">
-        <v>196</v>
+        <v>274</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>42</v>
       </c>
       <c r="C13" t="n">
-        <v>84</v>
+        <v>142</v>
       </c>
       <c r="D13" t="n">
-        <v>168</v>
+        <v>234</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>128</v>
       </c>
       <c r="D14" t="n">
-        <v>145</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>127</v>
       </c>
       <c r="D15" t="n">
-        <v>117</v>
+        <v>171</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>124</v>
       </c>
       <c r="D16" t="n">
-        <v>97</v>
+        <v>140</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C17" t="n">
-        <v>66</v>
+        <v>119</v>
       </c>
       <c r="D17" t="n">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C18" t="n">
-        <v>63</v>
+        <v>116</v>
       </c>
       <c r="D18" t="n">
-        <v>57</v>
+        <v>85</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="C19" t="n">
-        <v>60</v>
+        <v>111</v>
       </c>
       <c r="D19" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>109</v>
       </c>
       <c r="D20" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21">
@@ -4156,10 +4156,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C21" t="n">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="D21" t="n">
         <v>1</v>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2292</v>
+        <v>596</v>
       </c>
       <c r="C2" t="n">
-        <v>3440</v>
+        <v>19994</v>
       </c>
       <c r="D2" t="n">
-        <v>6022</v>
+        <v>11185</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2732</v>
+        <v>258</v>
       </c>
       <c r="C3" t="n">
-        <v>4513</v>
+        <v>9535</v>
       </c>
       <c r="D3" t="n">
-        <v>13454</v>
+        <v>7012</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3100</v>
+        <v>300</v>
       </c>
       <c r="C4" t="n">
-        <v>6663</v>
+        <v>4789</v>
       </c>
       <c r="D4" t="n">
-        <v>12587</v>
+        <v>6443</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1337</v>
+        <v>455</v>
       </c>
       <c r="C5" t="n">
-        <v>9623</v>
+        <v>5981</v>
       </c>
       <c r="D5" t="n">
-        <v>6200</v>
+        <v>4952</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>456</v>
+        <v>424</v>
       </c>
       <c r="C6" t="n">
-        <v>6980</v>
+        <v>7412</v>
       </c>
       <c r="D6" t="n">
-        <v>2015</v>
+        <v>2660</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>95</v>
+        <v>240</v>
       </c>
       <c r="C7" t="n">
-        <v>3149</v>
+        <v>6968</v>
       </c>
       <c r="D7" t="n">
-        <v>556</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>82</v>
       </c>
       <c r="C8" t="n">
-        <v>1173</v>
+        <v>4468</v>
       </c>
       <c r="D8" t="n">
-        <v>295</v>
+        <v>461</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
-        <v>346</v>
+        <v>1934</v>
       </c>
       <c r="D9" t="n">
-        <v>182</v>
+        <v>241</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C10" t="n">
-        <v>152</v>
+        <v>600</v>
       </c>
       <c r="D10" t="n">
-        <v>137</v>
+        <v>154</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>89</v>
+        <v>193</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="D12" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="D13" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D14" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>66</v>
+        <v>30</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6199</v>
+        <v>5552</v>
       </c>
       <c r="C2" t="n">
-        <v>7275</v>
+        <v>11795</v>
       </c>
       <c r="D2" t="n">
-        <v>18081</v>
+        <v>23603</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2408</v>
+        <v>767</v>
       </c>
       <c r="C3" t="n">
-        <v>3060</v>
+        <v>5769</v>
       </c>
       <c r="D3" t="n">
-        <v>1869</v>
+        <v>3583</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="C4" t="n">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="D4" t="n">
-        <v>1538</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>191</v>
+        <v>149</v>
       </c>
       <c r="C5" t="n">
-        <v>384</v>
+        <v>338</v>
       </c>
       <c r="D5" t="n">
-        <v>1161</v>
+        <v>986</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>202</v>
+        <v>141</v>
       </c>
       <c r="C6" t="n">
-        <v>459</v>
+        <v>356</v>
       </c>
       <c r="D6" t="n">
-        <v>808</v>
+        <v>712</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>145</v>
+        <v>102</v>
       </c>
       <c r="C7" t="n">
-        <v>350</v>
+        <v>277</v>
       </c>
       <c r="D7" t="n">
-        <v>546</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>105</v>
+        <v>78</v>
       </c>
       <c r="C8" t="n">
-        <v>260</v>
+        <v>206</v>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>384</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="C9" t="n">
-        <v>205</v>
+        <v>169</v>
       </c>
       <c r="D9" t="n">
-        <v>354</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="C10" t="n">
-        <v>180</v>
+        <v>153</v>
       </c>
       <c r="D10" t="n">
-        <v>356</v>
+        <v>324</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C11" t="n">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="D11" t="n">
-        <v>261</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="D12" t="n">
-        <v>199</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D13" t="n">
-        <v>170</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C15" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D15" t="n">
-        <v>118</v>
+        <v>111</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>77</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C18" t="n">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="D18" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="D21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5362</v>
+        <v>2647</v>
       </c>
       <c r="C2" t="n">
-        <v>7844</v>
+        <v>5498</v>
       </c>
       <c r="D2" t="n">
-        <v>21755</v>
+        <v>19086</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3534</v>
+        <v>2705</v>
       </c>
       <c r="C3" t="n">
-        <v>4695</v>
+        <v>8032</v>
       </c>
       <c r="D3" t="n">
-        <v>4455</v>
+        <v>6837</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1079</v>
+        <v>375</v>
       </c>
       <c r="C4" t="n">
-        <v>1835</v>
+        <v>3593</v>
       </c>
       <c r="D4" t="n">
-        <v>1557</v>
+        <v>1853</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>125</v>
+        <v>100</v>
       </c>
       <c r="C5" t="n">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="D5" t="n">
-        <v>1186</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>185</v>
+        <v>136</v>
       </c>
       <c r="C6" t="n">
-        <v>411</v>
+        <v>341</v>
       </c>
       <c r="D6" t="n">
-        <v>864</v>
+        <v>747</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>159</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>321</v>
       </c>
       <c r="D7" t="n">
-        <v>589</v>
+        <v>509</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="C8" t="n">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="D8" t="n">
-        <v>441</v>
+        <v>395</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C9" t="n">
-        <v>232</v>
+        <v>188</v>
       </c>
       <c r="D9" t="n">
-        <v>363</v>
+        <v>322</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="C10" t="n">
-        <v>190</v>
+        <v>161</v>
       </c>
       <c r="D10" t="n">
-        <v>352</v>
+        <v>315</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>166</v>
+        <v>140</v>
       </c>
       <c r="D11" t="n">
-        <v>270</v>
+        <v>244</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="D12" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="D13" t="n">
-        <v>172</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="D14" t="n">
-        <v>146</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C15" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C16" t="n">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="D16" t="n">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>78</v>
+        <v>73</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>9</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C21" t="n">
-        <v>106</v>
+        <v>92</v>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4380</v>
+        <v>2073</v>
       </c>
       <c r="C2" t="n">
-        <v>7083</v>
+        <v>7628</v>
       </c>
       <c r="D2" t="n">
-        <v>25161</v>
+        <v>20021</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3637</v>
+        <v>2209</v>
       </c>
       <c r="C3" t="n">
-        <v>5550</v>
+        <v>5734</v>
       </c>
       <c r="D3" t="n">
-        <v>6902</v>
+        <v>8391</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1962</v>
+        <v>1338</v>
       </c>
       <c r="C4" t="n">
-        <v>3416</v>
+        <v>6083</v>
       </c>
       <c r="D4" t="n">
-        <v>2066</v>
+        <v>2801</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>494</v>
+        <v>204</v>
       </c>
       <c r="C5" t="n">
-        <v>1099</v>
+        <v>2153</v>
       </c>
       <c r="D5" t="n">
-        <v>1206</v>
+        <v>1170</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>112</v>
       </c>
       <c r="C6" t="n">
-        <v>301</v>
+        <v>263</v>
       </c>
       <c r="D6" t="n">
-        <v>910</v>
+        <v>784</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>158</v>
+        <v>116</v>
       </c>
       <c r="C7" t="n">
-        <v>409</v>
+        <v>331</v>
       </c>
       <c r="D7" t="n">
-        <v>625</v>
+        <v>548</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>125</v>
+        <v>89</v>
       </c>
       <c r="C8" t="n">
-        <v>358</v>
+        <v>284</v>
       </c>
       <c r="D8" t="n">
-        <v>462</v>
+        <v>411</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>90</v>
+        <v>67</v>
       </c>
       <c r="C9" t="n">
-        <v>268</v>
+        <v>216</v>
       </c>
       <c r="D9" t="n">
-        <v>372</v>
+        <v>327</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>67</v>
+        <v>51</v>
       </c>
       <c r="C10" t="n">
-        <v>207</v>
+        <v>174</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C11" t="n">
-        <v>176</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>280</v>
+        <v>252</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="D12" t="n">
-        <v>213</v>
+        <v>191</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="D15" t="n">
-        <v>120</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C19" t="n">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>8</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" t="n">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4395</v>
+        <v>1596</v>
       </c>
       <c r="C2" t="n">
-        <v>6181</v>
+        <v>7549</v>
       </c>
       <c r="D2" t="n">
-        <v>27494</v>
+        <v>17351</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3289</v>
+        <v>1772</v>
       </c>
       <c r="C3" t="n">
-        <v>5517</v>
+        <v>5851</v>
       </c>
       <c r="D3" t="n">
-        <v>9191</v>
+        <v>9647</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2375</v>
+        <v>1526</v>
       </c>
       <c r="C4" t="n">
-        <v>4492</v>
+        <v>5762</v>
       </c>
       <c r="D4" t="n">
-        <v>2885</v>
+        <v>3789</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1007</v>
+        <v>639</v>
       </c>
       <c r="C5" t="n">
-        <v>2266</v>
+        <v>4200</v>
       </c>
       <c r="D5" t="n">
-        <v>1306</v>
+        <v>1431</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>280</v>
+        <v>142</v>
       </c>
       <c r="C6" t="n">
-        <v>703</v>
+        <v>1257</v>
       </c>
       <c r="D6" t="n">
-        <v>948</v>
+        <v>832</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>143</v>
+        <v>107</v>
       </c>
       <c r="C7" t="n">
-        <v>354</v>
+        <v>295</v>
       </c>
       <c r="D7" t="n">
-        <v>659</v>
+        <v>584</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>130</v>
+        <v>94</v>
       </c>
       <c r="C8" t="n">
-        <v>378</v>
+        <v>307</v>
       </c>
       <c r="D8" t="n">
-        <v>484</v>
+        <v>425</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="C9" t="n">
-        <v>310</v>
+        <v>248</v>
       </c>
       <c r="D9" t="n">
-        <v>378</v>
+        <v>337</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="C10" t="n">
-        <v>234</v>
+        <v>193</v>
       </c>
       <c r="D10" t="n">
-        <v>346</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="C11" t="n">
-        <v>187</v>
+        <v>159</v>
       </c>
       <c r="D11" t="n">
-        <v>286</v>
+        <v>255</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>159</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>217</v>
+        <v>198</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>128</v>
+        <v>108</v>
       </c>
       <c r="D13" t="n">
-        <v>176</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>99</v>
+        <v>85</v>
       </c>
       <c r="D14" t="n">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>122</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C17" t="n">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="D17" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" t="n">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C19" t="n">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>7</v>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="D20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C21" t="n">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5084</v>
+        <v>1340</v>
       </c>
       <c r="C2" t="n">
-        <v>7176</v>
+        <v>10239</v>
       </c>
       <c r="D2" t="n">
-        <v>32843</v>
+        <v>15310</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>2787</v>
+        <v>1402</v>
       </c>
       <c r="C3" t="n">
-        <v>4797</v>
+        <v>5849</v>
       </c>
       <c r="D3" t="n">
-        <v>10655</v>
+        <v>10138</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1747</v>
+        <v>1422</v>
       </c>
       <c r="C4" t="n">
-        <v>4142</v>
+        <v>5689</v>
       </c>
       <c r="D4" t="n">
-        <v>3445</v>
+        <v>4742</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>884</v>
+        <v>908</v>
       </c>
       <c r="C5" t="n">
-        <v>2484</v>
+        <v>4907</v>
       </c>
       <c r="D5" t="n">
-        <v>1236</v>
+        <v>1794</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>302</v>
+        <v>331</v>
       </c>
       <c r="C6" t="n">
-        <v>1004</v>
+        <v>2672</v>
       </c>
       <c r="D6" t="n">
-        <v>768</v>
+        <v>910</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="C7" t="n">
-        <v>333</v>
+        <v>766</v>
       </c>
       <c r="D7" t="n">
-        <v>513</v>
+        <v>619</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>58</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>223</v>
+        <v>301</v>
       </c>
       <c r="D8" t="n">
-        <v>364</v>
+        <v>441</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="C9" t="n">
-        <v>199</v>
+        <v>274</v>
       </c>
       <c r="D9" t="n">
-        <v>270</v>
+        <v>347</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="C10" t="n">
-        <v>150</v>
+        <v>216</v>
       </c>
       <c r="D10" t="n">
-        <v>237</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>41</v>
       </c>
       <c r="C11" t="n">
-        <v>114</v>
+        <v>171</v>
       </c>
       <c r="D11" t="n">
-        <v>194</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="C12" t="n">
-        <v>91</v>
+        <v>144</v>
       </c>
       <c r="D12" t="n">
-        <v>148</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>74</v>
+        <v>118</v>
       </c>
       <c r="D13" t="n">
-        <v>117</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="D14" t="n">
-        <v>96</v>
+        <v>135</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C16" t="n">
-        <v>38</v>
+        <v>67</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C17" t="n">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="D17" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>75</v>
+        <v>132</v>
       </c>
       <c r="D21" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5038</v>
+        <v>1820</v>
       </c>
       <c r="C2" t="n">
-        <v>8449</v>
+        <v>9376</v>
       </c>
       <c r="D2" t="n">
-        <v>28409</v>
+        <v>17379</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3271</v>
+        <v>1141</v>
       </c>
       <c r="C3" t="n">
-        <v>5320</v>
+        <v>6928</v>
       </c>
       <c r="D3" t="n">
-        <v>13598</v>
+        <v>10160</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1987</v>
+        <v>1228</v>
       </c>
       <c r="C4" t="n">
-        <v>4451</v>
+        <v>5594</v>
       </c>
       <c r="D4" t="n">
-        <v>4760</v>
+        <v>5432</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1175</v>
+        <v>1000</v>
       </c>
       <c r="C5" t="n">
-        <v>3403</v>
+        <v>5180</v>
       </c>
       <c r="D5" t="n">
-        <v>1643</v>
+        <v>2220</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>545</v>
+        <v>525</v>
       </c>
       <c r="C6" t="n">
-        <v>1820</v>
+        <v>3675</v>
       </c>
       <c r="D6" t="n">
-        <v>846</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="C7" t="n">
-        <v>714</v>
+        <v>1617</v>
       </c>
       <c r="D7" t="n">
-        <v>550</v>
+        <v>658</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>68</v>
+        <v>93</v>
       </c>
       <c r="C8" t="n">
-        <v>283</v>
+        <v>505</v>
       </c>
       <c r="D8" t="n">
-        <v>388</v>
+        <v>458</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>47</v>
+        <v>76</v>
       </c>
       <c r="C9" t="n">
-        <v>211</v>
+        <v>285</v>
       </c>
       <c r="D9" t="n">
-        <v>281</v>
+        <v>357</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C10" t="n">
-        <v>174</v>
+        <v>237</v>
       </c>
       <c r="D10" t="n">
-        <v>240</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="C11" t="n">
-        <v>131</v>
+        <v>188</v>
       </c>
       <c r="D11" t="n">
-        <v>199</v>
+        <v>258</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C12" t="n">
-        <v>101</v>
+        <v>153</v>
       </c>
       <c r="D12" t="n">
-        <v>152</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
-        <v>81</v>
+        <v>125</v>
       </c>
       <c r="D13" t="n">
-        <v>120</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="D14" t="n">
-        <v>98</v>
+        <v>136</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C15" t="n">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C16" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="D17" t="n">
-        <v>51</v>
+        <v>75</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C21" t="n">
-        <v>83</v>
+        <v>143</v>
       </c>
       <c r="D21" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4115</v>
+        <v>1650</v>
       </c>
       <c r="C2" t="n">
-        <v>8455</v>
+        <v>5925</v>
       </c>
       <c r="D2" t="n">
-        <v>27833</v>
+        <v>13820</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>3396</v>
+        <v>1823</v>
       </c>
       <c r="C3" t="n">
-        <v>6081</v>
+        <v>10159</v>
       </c>
       <c r="D3" t="n">
-        <v>14988</v>
+        <v>11401</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2262</v>
+        <v>924</v>
       </c>
       <c r="C4" t="n">
-        <v>4850</v>
+        <v>8409</v>
       </c>
       <c r="D4" t="n">
-        <v>6312</v>
+        <v>5142</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>1381</v>
+        <v>485</v>
       </c>
       <c r="C5" t="n">
-        <v>3905</v>
+        <v>3601</v>
       </c>
       <c r="D5" t="n">
-        <v>2145</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>781</v>
+        <v>168</v>
       </c>
       <c r="C6" t="n">
-        <v>2617</v>
+        <v>1584</v>
       </c>
       <c r="D6" t="n">
-        <v>979</v>
+        <v>644</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>315</v>
+        <v>85</v>
       </c>
       <c r="C7" t="n">
-        <v>1299</v>
+        <v>494</v>
       </c>
       <c r="D7" t="n">
-        <v>591</v>
+        <v>448</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>108</v>
+        <v>70</v>
       </c>
       <c r="C8" t="n">
-        <v>502</v>
+        <v>279</v>
       </c>
       <c r="D8" t="n">
-        <v>412</v>
+        <v>349</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C9" t="n">
-        <v>246</v>
+        <v>232</v>
       </c>
       <c r="D9" t="n">
-        <v>295</v>
+        <v>305</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C10" t="n">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="D10" t="n">
-        <v>241</v>
+        <v>252</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D11" t="n">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="D12" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="D13" t="n">
-        <v>121</v>
+        <v>133</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C14" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="D14" t="n">
-        <v>100</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C15" t="n">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C16" t="n">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D17" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="18">
@@ -6602,13 +6602,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C18" t="n">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C19" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="D19" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C20" t="n">
-        <v>28</v>
+        <v>143</v>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
